--- a/quizzes/sculpture-19e.xlsx
+++ b/quizzes/sculpture-19e.xlsx
@@ -4036,7 +4036,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art, MET</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art, MET</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">

--- a/quizzes/sculpture-19e.xlsx
+++ b/quizzes/sculpture-19e.xlsx
@@ -526,52 +526,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/a/a7/Pythia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/38/Socrates_dying_by_Mark_Antokolsky2.jpg/1280px-Socrates_dying_by_Mark_Antokolsky2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Adèle</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>d'AFFRY</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MARCELLO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MARCELLO</t>
+          <t>ANTOKOLSKY</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1875</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Saint-Pétersbourg</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Opéra de Paris</t>
+          <t>Musée russe</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>"Pythie"</t>
+          <t>"Mort de Socrate"</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -579,139 +574,139 @@
           <t>Marbre</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>c.200 cm</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>suisse</t>
+          <t>russe</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/f/f5/Fountain_On_Lenbachplatz_-_panoramio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=de</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/08/MAntokolski_IvanIV.JPG/960px-MAntokolski_IvanIV.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adolf</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>von HILDEBRAND</t>
+          <t>ANTOKOLSKY</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1893-1895</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Saint-Pétersbourg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Lenbachplatz</t>
+          <t>Musée russe</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>"Fontaine Wittelsbach (Wittelsbacherbrunnen)"</t>
+          <t>"Ivan le terrible"</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pierre et bronze</t>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>c.200 cm</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>russe</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8b/Hirtenknabe.jpg/960px-Hirtenknabe.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/a/a8/MAntokolsky_Mefisto.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Adolf</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>von HILDEBRAND</t>
+          <t>ANTOKOLSKY</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1871-1873</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Saint-Pétersbourg</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Alte Nationalgalerie</t>
+          <t>Musée russe</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>"Jeune pâtre endormi"</t>
+          <t>"Méphistophélès"</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>c.90 cm</t>
+          <t>c.60 cm</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>russe</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -721,17 +716,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ad/Alise-Sainte-Reine_-_Statue_de_Vercing%C3%A9torix_-_01.jpg/960px-Alise-Sainte-Reine_-_Statue_de_Vercing%C3%A9torix_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/b/b4/Emancipation_memorial_MRD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aimé</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MILLET</t>
+          <t>BALL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -741,72 +736,72 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>site d'Alésia</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Alise-Sainte-Reine</t>
+          <t>Lincoln Park</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>"Statue de Vercingétorix"</t>
+          <t>"Monument à l'émancipation (Emancipation Memorial)"</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Cuivre repoussé</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/1/15/Apollon_opera_Garnier_n3.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/dd/Barrias_La_Nature_se_d%C3%A9voilant.jpg/1920px-Barrias_La_Nature_se_d%C3%A9voilant.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aimé</t>
+          <t>Louis-Ernest</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MILLET</t>
+          <t>BARRIAS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1860-1869</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -816,17 +811,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Palais Garnier</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>"Apollon, la Poésie et la Musique. Toit du Palais Garnier"</t>
+          <t>"La Nature se dévoilant à la Science"</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Cuivre doré</t>
+          <t>Marbre, onyx et bronze</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>c.200 cm</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -835,38 +835,38 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Paris_-_Mus%C3%A9e_d%27Orsay_8503.jpg/960px-Paris_-_Mus%C3%A9e_d%27Orsay_8503.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c4/La_D%C3%A9fense_de_Paris_%40_Parvis_%40_La_D%C3%A9fense_%40_Paris_%2834342635104%29.jpg/1920px-La_D%C3%A9fense_de_Paris_%40_Parvis_%40_La_D%C3%A9fense_%40_Paris_%2834342635104%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Albert-Ernest</t>
+          <t>Louis-Ernest</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CARRIER-BELLEUSE</t>
+          <t>BARRIAS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -876,22 +876,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Rond-point de la Défense</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>"La Bacchante"</t>
+          <t>"La Défense de Paris"</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>c.90 cm</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -900,63 +895,53 @@
         </is>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/CB_H%C3%A9b%C3%A9.jpg/960px-CB_H%C3%A9b%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f3/Statue-de-la-liberte-new-york.jpg/960px-Statue-de-la-liberte-new-york.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Albert-Ernest</t>
+          <t>Auguste</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CARRIER-BELLEUSE</t>
+          <t>BARTHOLDI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Paris</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>"Hébé endormie"</t>
+          <t>"La Liberté éclairant le monde."</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>c.60 cm</t>
+          <t>Cuivre repoussé (structure Eiffel)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -965,58 +950,53 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5a/Torch%C3%A8re_du_grand_escalier_du_palais_Garnier_par_Carrier_Belleuse.jpg/960px-Torch%C3%A8re_du_grand_escalier_du_palais_Garnier_par_Carrier_Belleuse.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/2/27/LionBelfort.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Albert-Ernest</t>
+          <t>Auguste</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CARRIER-BELLEUSE</t>
+          <t>BARTHOLDI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Paris</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Palais Garnier</t>
+          <t>Belfort</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>"Une des torchères du grand escalier de l'Opéra de Paris."</t>
+          <t>"Le Lion de Belfort"</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bronze doré</t>
+          <t>Grès rose</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1031,32 +1011,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Alexandre_Falgui%C3%A8re_-_Vainqueur_au_combat_de_coqs_%281864%29.jpg/1280px-Alexandre_Falgui%C3%A8re_-_Vainqueur_au_combat_de_coqs_%281864%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ed/Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG/1280px-Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FALGUIÈRE</t>
+          <t>BARTOLINI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1837-1845</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1066,12 +1046,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>"Vainqueur au combat de coqs"</t>
+          <t>"Nymphe au scorpion"</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1081,47 +1061,52 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>c.90 cm</t>
+          <t>80 cm</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>180 cm</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f1/Statue-Orsay-03.jpg/1280px-Statue-Orsay-03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG/1280px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Antoine-Louis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FALGUIÈRE</t>
+          <t>BARYE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1131,22 +1116,27 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>"Tarcisius, martyr chrétien"</t>
+          <t>"Lion au serpent"</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>c.60 cm</t>
+          <t>135 cm</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>178 cm</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1155,58 +1145,58 @@
         </is>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/7/78/Falguiere_Asie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/a/ac/%27Theseus_Fighting_the_Minotaur%27_by_Antoine-Louis_Barye%2C_Dayton.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Antoine-Louis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FALGUIÈRE</t>
+          <t>BARYE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1878</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Paris</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Dayton Art Institute</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>"L'Asie"</t>
+          <t>"Thésée et le Minotaure"</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bronze</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>c.45 cm</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1221,127 +1211,107 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a6/A_la_terre_Boucher_MBA_Rennes.jpg/1920px-A_la_terre_Boucher_MBA_Rennes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/69/Neptunbrunnen_Berlin_2.jpg/1280px-Neptunbrunnen_Berlin_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alfred</t>
+          <t>Reinhold</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BOUCHER</t>
+          <t>BEGAS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1890</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Rennes</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Musée des Beaux-Arts</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>"A la terre"</t>
+          <t>"Neptunbrunnen (Fontaine de Neptune)"</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>c.60 cm</t>
+          <t>Bronze et marbre</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Au_But_%28Alfred_Boucher%29_01.jpg/1280px-Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Au_But_%28Alfred_Boucher%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/73/Schillerdenkmal_Berlin_Gendarmenmarkt_Begas_1.jpg/960px-Schillerdenkmal_Berlin_Gendarmenmarkt_Begas_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alfred</t>
+          <t>Reinhold</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BOUCHER</t>
+          <t>BEGAS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1886</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Aix-les-Bains</t>
+          <t>1862-1871</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Musée Faure</t>
+          <t>Gendarmenmarkt à Berlin</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>"Au But!"</t>
+          <t>"Mémorial Schiller"</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>c.190 cm</t>
+          <t>Bronze et marbre</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U14" t="n">
@@ -1351,57 +1321,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Piccadilly.jpg/960px-Piccadilly.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/30/Nymphe_Salmacis_Bosio_Louvre_LP1307.jpg/960px-Nymphe_Salmacis_Bosio_Louvre_LP1307.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alfred</t>
+          <t>François Joseph</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GILBERT</t>
+          <t>BOSIO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Piccadilly Circus</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>"La Fontaine d'Éros"</t>
+          <t>"La Nymphe Salmacis"</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bronze doré et aluminium</t>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>c.150 cm</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U15" t="n">
@@ -1411,7 +1386,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/86/Cathedral_Church_of_St_Paul%2C_Monument_to_the_1st_Duke_of_Wellington_City_of_London_1079157_20230822_0197.jpg/960px-Cathedral_Church_of_St_Paul%2C_Monument_to_the_1st_Duke_of_Wellington_City_of_London_1079157_20230822_0197.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a6/A_la_terre_Boucher_MBA_Rennes.jpg/1920px-A_la_terre_Boucher_MBA_Rennes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1421,47 +1396,52 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>STEVENS</t>
+          <t>BOUCHER</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Paul</t>
+          <t>Musée des Beaux-Arts</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>"Monument au duc de Wellington"</t>
+          <t>"A la terre"</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Marbre et bronze</t>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>c.60 cm</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U16" t="n">
@@ -1471,117 +1451,127 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5a/U.S._Capitol_Samuel_Adams_Statue.jpg/960px-U.S._Capitol_Samuel_Adams_Statue.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Au_But_%28Alfred_Boucher%29_01.jpg/1280px-Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Au_But_%28Alfred_Boucher%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Alfred</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>WHITNEY</t>
+          <t>BOUCHER</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Aix-les-Bains</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>United States Capitol</t>
+          <t>Musée Faure</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>"Samuel Adams"</t>
+          <t>"Au But!"</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>c.190 cm</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/32/Arc_de_Triomphe%2C_la_R%C3%A9sistance_de_1814%2C_Antoine_Etex.jpg/960px-Arc_de_Triomphe%2C_la_R%C3%A9sistance_de_1814%2C_Antoine_Etex.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Theseus_and_Centaur_by_Antonio_Canova_1.jpg/1280px-Theseus_and_Centaur_by_Antonio_Canova_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Antoine</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ETEX</t>
+          <t>CANOVA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Vienne</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Arc de Triomphe</t>
+          <t>Kunsthistorischen Museum</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>"La Résistance de 1814"</t>
+          <t>"Thésée et le Centaure"</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>c.340 cm</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U18" t="n">
@@ -1591,92 +1581,87 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG/1280px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Antonio_Canova%2C_Endymion_%281%29.JPG/1280px-Antonio_Canova%2C_Endymion_%281%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Antoine-Louis</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BARYE</t>
+          <t>CANOVA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Bakewell</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Chatsworth House</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>"Lion au serpent"</t>
+          <t>"Endymion dormant"</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>135 cm</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>178 cm</t>
+          <t>c.105 cm</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/a/ac/%27Theseus_Fighting_the_Minotaur%27_by_Antoine-Louis_Barye%2C_Dayton.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG/960px-Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Antoine-Louis</t>
+          <t>Jean-Baptiste</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BARYE</t>
+          <t>CARPEAUX</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1686,27 +1671,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1869</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Dayton Art Institute</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>"Thésée et le Minotaure"</t>
+          <t>"La Danse (façade de l'Opéra de Paris)"</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>c.45 cm</t>
+          <t>Pierre</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -1715,38 +1700,38 @@
         </is>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/2/25/David-Antonin_Mercie-IMG_8380-white.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg/1280px-20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=lt</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Antonin</t>
+          <t>Jean-Baptiste</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MERCIÉ</t>
+          <t>CARPEAUX</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1756,22 +1741,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Jardin des Grands Explorateurs (de l'Observatoire)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>"David"</t>
+          <t>"Fontaine des Quatre-Parties-du-Monde"</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bronze</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>c.180 cm</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -1786,32 +1766,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8f/Gloria_Victis_-_Anthonin_Merci%C3%A9.jpg/960px-Gloria_Victis_-_Anthonin_Merci%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1a/Ugolino_Carpeaux_Petit_Palais_PPSO1573.jpg/960px-Ugolino_Carpeaux_Petit_Palais_PPSO1573.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Antonin</t>
+          <t>Jean-Baptiste</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MERCIÉ</t>
+          <t>CARPEAUX</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1857-1861</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1821,12 +1801,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Musée du Petit Palais</t>
+          <t>Petit Palais</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>"Gloria Victis"</t>
+          <t>"Ugolin entouré de ses quatre enfants,"</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -1834,64 +1814,59 @@
           <t>Bronze</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>c.280 cm</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>française</t>
         </is>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Theseus_and_Centaur_by_Antonio_Canova_1.jpg/1280px-Theseus_and_Centaur_by_Antonio_Canova_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Paris_-_Mus%C3%A9e_d%27Orsay_8503.jpg/960px-Paris_-_Mus%C3%A9e_d%27Orsay_8503.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Albert-Ernest</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CANOVA</t>
+          <t>CARRIER-BELLEUSE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Vienne</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Kunsthistorischen Museum</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>"Thésée et le Centaure"</t>
+          <t>"La Bacchante"</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -1901,62 +1876,62 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>c.340 cm</t>
+          <t>c.90 cm</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Antonio_Canova%2C_Endymion_%281%29.JPG/1280px-Antonio_Canova%2C_Endymion_%281%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/CB_H%C3%A9b%C3%A9.jpg/960px-CB_H%C3%A9b%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Albert-Ernest</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CANOVA</t>
+          <t>CARRIER-BELLEUSE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Bakewell</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Chatsworth House</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>"Endymion dormant"</t>
+          <t>"Hébé endormie"</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -1966,12 +1941,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>c.105 cm</t>
+          <t>c.60 cm</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U24" t="n">
@@ -1981,47 +1956,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f3/Statue-de-la-liberte-new-york.jpg/960px-Statue-de-la-liberte-new-york.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5a/Torch%C3%A8re_du_grand_escalier_du_palais_Garnier_par_Carrier_Belleuse.jpg/960px-Torch%C3%A8re_du_grand_escalier_du_palais_Garnier_par_Carrier_Belleuse.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Auguste</t>
+          <t>Albert-Ernest</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BARTHOLDI</t>
+          <t>CARRIER-BELLEUSE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1873</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Palais Garnier</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>"La Liberté éclairant le monde."</t>
+          <t>"Une des torchères du grand escalier de l'Opéra de Paris."</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Cuivre repoussé (structure Eiffel)</t>
+          <t>Bronze doré</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -2030,58 +2010,58 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/2/27/LionBelfort.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/19/Chantreys_Sleeping_Children.jpg/1280px-Chantreys_Sleeping_Children.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Auguste</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BARTHOLDI</t>
+          <t>CHANTREY</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Belfort</t>
+          <t>Cathédrale de Lichfield</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>"Le Lion de Belfort"</t>
+          <t>"Enfants endormis"</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grès rose</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U26" t="n">
@@ -2091,32 +2071,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5f/Pr%C3%A9ault_-_Le_Silence_-_Robl%C3%A8s_01.jpg/960px-Pr%C3%A9ault_-_Le_Silence_-_Robl%C3%A8s_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d5/La_Jeunesse%2C_S3494%2801%29.jpg/960px-La_Jeunesse%2C_S3494%2801%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Auguste</t>
+          <t>Henri</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PRÉAULT</t>
+          <t>CHAPU</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2126,22 +2106,22 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Cimetière du Père-Lachaise</t>
+          <t>Musée Carnavalet</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>"Le Silence"</t>
+          <t>"La Jeunesse"</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>c.40 cm</t>
+          <t>c.150 cm</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -2156,32 +2136,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Le_Penseur_Mus%C3%A9e_Rodin_Paris_S.1295.jpg/960px-Le_Penseur_Mus%C3%A9e_Rodin_Paris_S.1295.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e5/Henri_Chapu_-_Jeanne_d%27Arc.jpg/960px-Henri_Chapu_-_Jeanne_d%27Arc.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Auguste</t>
+          <t>Henri</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RODIN</t>
+          <t>CHAPU</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1880-1904</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2191,22 +2171,22 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Musée Rodin</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>"Le Penseur"</t>
+          <t>"Jeanne d’Arc à Domremy"</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>189 cm</t>
+          <t>c.190 cm</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -2215,38 +2195,38 @@
         </is>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/2018_Balzac_%281898%29_1.jpg/960px-2018_Balzac_%281898%29_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Le_Masque-Ernest_Christophe-IMG_8124-black.jpg/1920px-Le_Masque-Ernest_Christophe-IMG_8124-black.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Auguste</t>
+          <t>Ernest</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RODIN</t>
+          <t>CHRISTOPHE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2256,22 +2236,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Musée Rodin</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>"Monument à Balzac"</t>
+          <t>"La Comédie humaine (dit aussi Le Masque)"</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>270 cm</t>
+          <t>c.190 cm</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -2280,53 +2260,53 @@
         </is>
       </c>
       <c r="U29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/04/Statue_bourgeois_calais_rodin.jpg/1280px-Statue_bourgeois_calais_rodin.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg/960px-La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Auguste</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>RODIN</t>
+          <t>CLAUDEL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1884-1895</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Calais</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Place de l’hôtel de ville</t>
+          <t>Musée Rodin</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>"Les Bourgeois de Calais"</t>
+          <t>"La Valse"</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2336,7 +2316,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>217 cm</t>
+          <t>c.90 cm</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -2345,38 +2325,38 @@
         </is>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Rodin_-_Le_Baiser_06.jpg/960px-Rodin_-_Le_Baiser_06.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Rodin_et_Musee_d%27Orsay_43_%2812176737546%29.jpg/960px-Rodin_et_Musee_d%27Orsay_43_%2812176737546%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Auguste</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RODIN</t>
+          <t>CLAUDEL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1881-1882</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2391,12 +2371,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>"Le Baiser"</t>
+          <t>"La Vague"</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze, marbre et onyx</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>c.62 cm</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -2411,57 +2396,52 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/7/77/Rodin_The_bronze_age.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/Claudel-2014-05.jpg/1280px-Claudel-2014-05.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Auguste</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RODIN</t>
+          <t>CLAUDEL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Alte Nationalgalerie</t>
+          <t>Musée Rodin</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>"L'Âge d'airain"</t>
+          <t>"L'Âge mûr"</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bronze</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>178 cm</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -2476,57 +2456,57 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG/1280px-Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Sculpture-7808948_%2852096525415%29.jpg/1280px-Sculpture-7808948_%2852096525415%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Augustus</t>
+          <t>Jean-Baptiste</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SAINT-GAUDENS</t>
+          <t>CLÉSINGER</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Boston Common</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>"Monument à Robert Gould Shaw et au 54e régiment du Massachusetts"</t>
+          <t>"La Femme piquée par un serpent"</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U33" t="n">
@@ -2536,47 +2516,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/Vor_Frue_Kirke_Copenhagen_altar.jpg/960px-Vor_Frue_Kirke_Copenhagen_altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/64/Chopin_Grave_Grab_Pere_Lachaise.JPG/960px-Chopin_Grave_Grab_Pere_Lachaise.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bertel</t>
+          <t>Jean-Baptiste</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>THORVALDSEN</t>
+          <t>CLÉSINGER</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1821</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Copenhague</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Cathédrale Notre-Dame (Vor Frue Kirke)</t>
+          <t>Cimetière du Père-Lachaise à Paris</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>"Le Christ"</t>
+          <t>"Monument funéraire de Frédéric Chopin"</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -2584,64 +2559,59 @@
           <t>Marbre</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>c.275 cm</t>
-        </is>
-      </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>danoise</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Jas%C3%A3o_e_o_Velo_de_ouro_-_Bertel_Thorvaldsen_-_1803.jpg/960px-Jas%C3%A3o_e_o_Velo_de_ouro_-_Bertel_Thorvaldsen_-_1803.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/6/64/Paris_8e_-_Petit_Palais_-_Mus%C3%A9e_des_Beaux-Arts_-_Bacchante_%28Auguste_Cl%C3%A9singer%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bertel</t>
+          <t>Jean-Baptiste</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>THORVALDSEN</t>
+          <t>CLÉSINGER</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Copenhague</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Musée Thorvaldsen</t>
+          <t>Petit Palais</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>"Jason à la Toison d'or"</t>
+          <t>"Bacchante couchée"</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -2649,14 +2619,9 @@
           <t>Marbre</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>242 cm</t>
-        </is>
-      </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>danoise</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U35" t="n">
@@ -2666,32 +2631,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg/960px-La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0b/Negre_du_Sudan_Charles_Cordier_Mus%C3%A9e_d%27Orsay.JPG/960px-Negre_du_Sudan_Charles_Cordier_Mus%C3%A9e_d%27Orsay.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLAUDEL</t>
+          <t>CORDIER</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1856-1857</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2701,17 +2666,17 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Musée Rodin</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>"La Valse"</t>
+          <t>"Homme du Soudan"</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Bronze et onyx polychrome</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -2725,38 +2690,38 @@
         </is>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Rodin_et_Musee_d%27Orsay_43_%2812176737546%29.jpg/960px-Rodin_et_Musee_d%27Orsay_43_%2812176737546%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/55/Statue_of_Gaspard_de_Coligny_%40_Paris_%2832269434936%29.jpg/960px-Statue_of_Gaspard_de_Coligny_%40_Paris_%2832269434936%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Gustave</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLAUDEL</t>
+          <t>CRAUK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2766,22 +2731,17 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Musée Rodin</t>
+          <t>Temple de l’Oratoire du Louvre</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>"La Vague"</t>
+          <t>"Statue de Gaspard de Coligny"</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bronze, marbre et onyx</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>c.62 cm</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -2790,98 +2750,108 @@
         </is>
       </c>
       <c r="U37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/Claudel-2014-05.jpg/1280px-Claudel-2014-05.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/a/a7/Pythia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Adèle</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLAUDEL</t>
+          <t>d'AFFRY</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MARCELLO</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>MARCELLO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1899</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Paris</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Musée Rodin</t>
+          <t>Opéra de Paris</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>"L'Âge mûr"</t>
+          <t>"Pythie"</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>c.200 cm</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>suisse</t>
         </is>
       </c>
       <c r="U38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0b/Negre_du_Sudan_Charles_Cordier_Mus%C3%A9e_d%27Orsay.JPG/960px-Negre_du_Sudan_Charles_Cordier_Mus%C3%A9e_d%27Orsay.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/57/Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg/960px-Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CORDIER</t>
+          <t>DALOU</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1856-1857</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2891,22 +2861,17 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Place de la Nation</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>"Homme du Soudan"</t>
+          <t>"Le Triomphe de la République"</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bronze et onyx polychrome</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>c.90 cm</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -2915,53 +2880,53 @@
         </is>
       </c>
       <c r="U39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/58/Berlin_Friedrich_II_Denkmal_09-2017_img1.jpg/960px-Berlin_Friedrich_II_Denkmal_09-2017_img1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/47/Dalou_paysan.jpg/960px-Dalou_paysan.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Christian Daniel</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RAUCH</t>
+          <t>DALOU</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1839-1851</t>
+          <t>1897-1902</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Unter den Linden</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>"Monument équestre à Frédéric le Grand"</t>
+          <t>"Grand paysan"</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -2969,144 +2934,169 @@
           <t>Bronze</t>
         </is>
       </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>c.100 cm</t>
+        </is>
+      </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f6/Belgique_-_Bruxelles_-_Botanique_-_L%27Automne_ou_Le_Semeur_de_Constantin_Meunier_-_01.jpg/960px-Belgique_-_Bruxelles_-_Botanique_-_L%27Automne_ou_Le_Semeur_de_Constantin_Meunier_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9a/Fronton_Panth%C3%A9on_Paris_1_reframed.jpg/1280px-Fronton_Panth%C3%A9on_Paris_1_reframed.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Constantin</t>
+          <t>Pierre-Jean</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MEUNIER</t>
+          <t>DAVID</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DAVID D'ANGERS</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DAVID D'ANGERS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1892-1896</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Bruxelles</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Jardin botanique</t>
+          <t>Panthéon</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>"Le Semeur (L'Automne)"</t>
+          <t>"Fronton du Panthéon de Paris"</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>c.220 cm</t>
+          <t>Pierre</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>belge</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7d/%D0%92%D0%B0%D1%80%D1%88%D0%B0%D0%B2%D0%B0_-_panoramio_%28130%29.jpg/960px-%D0%92%D0%B0%D1%80%D1%88%D0%B0%D0%B2%D0%B0_-_panoramio_%28130%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/af/Philopoemen_David_Angers_Louvre_LP1556.jpg/960px-Philopoemen_David_Angers_Louvre_LP1556.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cyprian</t>
+          <t>Pierre-Jean</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GODEBSKI</t>
+          <t>DAVID</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DAVID D'ANGERS</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>DAVID D'ANGERS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1897-1898</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Varsovie</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>"Monument à Adam Mickiewicz"</t>
+          <t>"Philopœmen blessé."</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bronze et pierre</t>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>c.250 cm</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>polonaise</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9a/Fronton_Panth%C3%A9on_Paris_1_reframed.jpg/1280px-Fronton_Panth%C3%A9on_Paris_1_reframed.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/David_d%27Angers_-_Barra.jpg/1280px-David_d%27Angers_-_Barra.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3141,27 +3131,32 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Panthéon</t>
+          <t>Galerie David d'Angers</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>"Fronton du Panthéon de Paris"</t>
+          <t>"Le jeune Barra"</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>c.60 cm</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -3170,73 +3165,63 @@
         </is>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/af/Philopoemen_David_Angers_Louvre_LP1556.jpg/960px-Philopoemen_David_Angers_Louvre_LP1556.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/e/ee/Edgar_degas%2C_little_dancer_aged_14%2C_1879-81.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pierre-Jean</t>
+          <t>Edgar</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DAVID</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>DAVID D'ANGERS</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>DAVID D'ANGERS</t>
+          <t>DEGAS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1878-1881</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>National Gallery of Art</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>"Philopœmen blessé."</t>
+          <t>"La Petite Danseuse de quatorze ans (1er modèle en cire)"</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Cire (original)</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>c.250 cm</t>
+          <t>98 cm</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -3245,73 +3230,58 @@
         </is>
       </c>
       <c r="U44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/David_d%27Angers_-_Barra.jpg/1280px-David_d%27Angers_-_Barra.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/25/LeTemps_fauchant_les_amours.jpg/500px-LeTemps_fauchant_les_amours.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pierre-Jean</t>
+          <t>Gustave</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DAVID</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>DAVID D'ANGERS</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>DAVID D'ANGERS</t>
+          <t>DORÉ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1839</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Angers</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Galerie David d'Angers</t>
+          <t>Musée des Arts décoratifs de Paris</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>"Le jeune Barra"</t>
+          <t>"LeTemps fauchant les amours"</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>c.60 cm</t>
+          <t>c.180 cm</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -3326,57 +3296,52 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/e/ee/Edgar_degas%2C_little_dancer_aged_14%2C_1879-81.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/Monument_Dumas%2C_Paris%2C_16_April_2022.jpg/960px-Monument_Dumas%2C_Paris%2C_16_April_2022.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Edgar</t>
+          <t>Gustave</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DEGAS</t>
+          <t>DORÉ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1878-1881</t>
+          <t>1882-1883</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>National Gallery of Art</t>
+          <t>Place du Général Catroux</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>"La Petite Danseuse de quatorze ans (1er modèle en cire)"</t>
+          <t>"Monument à Alexandre Dumas"</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Cire (original)</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>98 cm</t>
+          <t>Bronze et pierre</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -3385,118 +3350,128 @@
         </is>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/Edmonia_Lewis_-_The_death_of_Cleopatra.jpg/960px-Edmonia_Lewis_-_The_death_of_Cleopatra.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b1/Paul_Dubois_Chanteur_florentin.jpg/960px-Paul_Dubois_Chanteur_florentin.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Edmonia</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LEWIS</t>
+          <t>DUBOIS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Smithsonian American Art Museum</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>"La Mort de Cléopâtre"</t>
+          <t>"Le Chanteur florentin (Le Condottiere)"</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>c.160 cm</t>
+          <t>c.190 cm</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/0/02/Statue_of_Saint_Michael_and_the_dragon_%28Spire_of_Mont_Saint-Michel_Abbey%29_PA00110460_%286%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/3/32/Eve_naissante_Dubois_Petit_Palais_PPS00946.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Emmanuel</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FRÉMIET</t>
+          <t>DUBOIS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1873</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Abbaye du Mont-Saint-Michel</t>
+          <t>Petit Palais</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>"Saint Michel terrassant le Dragon"</t>
+          <t>"Ève naissante"</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Cuivre repoussé doré</t>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>c.175 cm</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -3511,52 +3486,52 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/8/80/Paris_8e_-_Pont_Alexandre_III_-_La_Renomm%C3%A9e_des_Arts_%28Emmanuel_Fr%C3%A9miet%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/Strasbourg_StMaurice_004.JPG/1280px-Strasbourg_StMaurice_004.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Emmanuel</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FRÉMIET</t>
+          <t>DUBOIS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1899-1900</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Pont Alexandre III</t>
+          <t>Église catholique Saint-Maurice</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>"La Renommée des Arts"</t>
+          <t>"Statue équestre de Jeanne d’Arc"</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bronze doré</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -3571,157 +3546,152 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/76/Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg/960px-Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/03/Giovanni_dupr%C3%A9%2C_abele_morente_01.jpg/1280px-Giovanni_dupr%C3%A9%2C_abele_morente_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Emmanuel</t>
+          <t>Giovanni</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FRÉMIET</t>
+          <t>DUPRÉ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1874</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Paris</t>
+          <t>1844-1951</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Place des Pyramides</t>
+          <t>Palazzo Pitti</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>"Statue de Jeanne d’Arc"</t>
+          <t>"Abel mourant"</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>c.170 cm</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg/960px-%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/7/74/Uffizi_Giotto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Emmanuel</t>
+          <t>Giovanni</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FRÉMIET</t>
+          <t>DUPRÉ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Musée des Beaux-Arts</t>
+          <t>Piazzale des Offices</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>"Gorille enlevant une femme"</t>
+          <t>"Statue de Giotto"</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>c.190 cm</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Le_Masque-Ernest_Christophe-IMG_8124-black.jpg/1920px-Le_Masque-Ernest_Christophe-IMG_8124-black.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/32/Arc_de_Triomphe%2C_la_R%C3%A9sistance_de_1814%2C_Antoine_Etex.jpg/960px-Arc_de_Triomphe%2C_la_R%C3%A9sistance_de_1814%2C_Antoine_Etex.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ernest</t>
+          <t>Antoine</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CHRISTOPHE</t>
+          <t>ETEX</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3731,22 +3701,17 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Arc de Triomphe</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>"La Comédie humaine (dit aussi Le Masque)"</t>
+          <t>"La Résistance de 1814"</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>c.190 cm</t>
+          <t>Pierre</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -3755,63 +3720,68 @@
         </is>
       </c>
       <c r="U52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f0/Denkmal_-_panoramio_%2864%29.jpg/960px-Denkmal_-_panoramio_%2864%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Alexandre_Falgui%C3%A8re_-_Vainqueur_au_combat_de_coqs_%281864%29.jpg/1280px-Alexandre_Falgui%C3%A8re_-_Vainqueur_au_combat_de_coqs_%281864%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ernst</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RIETSCHEL</t>
+          <t>FALGUIÈRE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Weimar</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Theaterplatz</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>"Monument à Goethe et Schiller"</t>
+          <t>"Vainqueur au combat de coqs"</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>c.90 cm</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U53" t="n">
@@ -3821,42 +3791,47 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/19/Chantreys_Sleeping_Children.jpg/1280px-Chantreys_Sleeping_Children.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f1/Statue-Orsay-03.jpg/1280px-Statue-Orsay-03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CHANTREY</t>
+          <t>FALGUIÈRE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>1868</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Cathédrale de Lichfield</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>"Enfants endormis"</t>
+          <t>"Tarcisius, martyr chrétien"</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -3864,9 +3839,14 @@
           <t>Marbre</t>
         </is>
       </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>c.60 cm</t>
+        </is>
+      </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U54" t="n">
@@ -3876,32 +3856,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/30/Nymphe_Salmacis_Bosio_Louvre_LP1307.jpg/960px-Nymphe_Salmacis_Bosio_Louvre_LP1307.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/7/78/Falguiere_Asie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>François Joseph</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BOSIO</t>
+          <t>FALGUIÈRE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3911,22 +3891,17 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>"La Nymphe Salmacis"</t>
+          <t>"L'Asie"</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>c.150 cm</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -3941,122 +3916,122 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg/960px-Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c0/PolyxenaFedi.jpg/960px-PolyxenaFedi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Pio</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RUDE</t>
+          <t>FEDI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Arc de Triomphe</t>
+          <t>Loggia dei Lanzi</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>"Le Départ des volontaires de 1792 (La Marseillaise)"</t>
+          <t>"L'Enlèvement de Polyxène"</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>c.250 cm</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/b/bb/Head_of_the_Old_Warrior_%28T%C3%AAte_du_Guerrier%29_MET_63761.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Pio_fedi%2C_monumento_funebre_a_Giovan_Battista_Niccolini%2C_1883%2C_02_personificazione_della_libert%C3%A0_della_poesia.jpg/960px-Pio_fedi%2C_monumento_funebre_a_Giovan_Battista_Niccolini%2C_1883%2C_02_personificazione_della_libert%C3%A0_della_poesia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Pio</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RUDE</t>
+          <t>FEDI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art</t>
+          <t>Basilique Santa Croce</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>"Tête du Guerrier"</t>
+          <t>"La Liberté de la Poésie"</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>c.40 cm</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U57" t="n">
@@ -4066,57 +4041,47 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/e/e2/David_Rude_Louvre_LP1780.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/0/02/Statue_of_Saint_Michael_and_the_dragon_%28Spire_of_Mont_Saint-Michel_Abbey%29_PA00110460_%286%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Emmanuel</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RUDE</t>
+          <t>FRÉMIET</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1831</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Paris</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Abbaye du Mont-Saint-Michel</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>"Buste du peintre français Jacques Louis David"</t>
+          <t>"Saint Michel terrassant le Dragon"</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>c.60 cm</t>
+          <t>Cuivre repoussé doré</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -4131,57 +4096,52 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9d/Mus%C3%A9e_et_Parc_Noisot_005.jpg/1280px-Mus%C3%A9e_et_Parc_Noisot_005.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/8/80/Paris_8e_-_Pont_Alexandre_III_-_La_Renomm%C3%A9e_des_Arts_%28Emmanuel_Fr%C3%A9miet%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Emmanuel</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>RUDE</t>
+          <t>FRÉMIET</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1899-1900</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Fixin</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Parc Noiset</t>
+          <t>Pont Alexandre III</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>"Napoléon s'éveillant à l'Immortalité"</t>
+          <t>"La Renommée des Arts"</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>c.250 cm</t>
+          <t>Bronze doré</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -4196,32 +4156,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Baptism_of_Christ%2C_%C3%89glise_de_la_Madeleine%2C_Paris_July_2011.jpg/1280px-Baptism_of_Christ%2C_%C3%89glise_de_la_Madeleine%2C_Paris_July_2011.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/76/Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg/960px-Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Emmanuel</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>RUDE</t>
+          <t>FRÉMIET</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4231,17 +4191,17 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Église de la Madeleine</t>
+          <t>Place des Pyramides</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>"Le Baptême du Christ"</t>
+          <t>"Statue de Jeanne d’Arc"</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -4256,57 +4216,57 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Art%26Archeologie_Valence063a_Fran%C3%A7ois_Rude.jpg/1280px-Art%26Archeologie_Valence063a_Fran%C3%A7ois_Rude.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg/960px-%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Emmanuel</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RUDE</t>
+          <t>FRÉMIET</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Valence</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Musée d’art et d’archéologie</t>
+          <t>Musée des Beaux-Arts</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>"Jeune pêcheur napolitain jouant avec une tortue"</t>
+          <t>"Gorille enlevant une femme"</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>c.82 cm</t>
+          <t>c.190 cm</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -4315,118 +4275,113 @@
         </is>
       </c>
       <c r="U61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9d/An_athlete_wrestling_a_python.png/960px-An_athlete_wrestling_a_python.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Chaire_Cath%C3%A9drale_Li%C3%A8ge_240809_03.jpg/960px-Chaire_Cath%C3%A9drale_Li%C3%A8ge_240809_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Frederic</t>
+          <t>Guillaume</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LEIGHTON</t>
+          <t>GEEFS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1877</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Londres</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Tate Britain</t>
+          <t>Cathédrale de Liège</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>"Athlète luttant avec un python"</t>
+          <t>"Le Génie du Mal"</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>c.175 cm</t>
+          <t>c.220 cm</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>belge</t>
         </is>
       </c>
       <c r="U62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/7/7d/Frederic_Leighton_-_The_Sluggard_-_B1982.17_-_Yale_Center_for_British_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original&amp;uselang=fr</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/9/94/The_Fisher_Boy_by_Vincenzo_Gemito%2C_Museo_del_Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Frederic</t>
+          <t>Vincenzo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LEIGHTON</t>
+          <t>GEMITO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Université de Yale</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Yale Center for British Art</t>
+          <t>Museo Nazionale del Bargello</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>"Le Paresseux"</t>
+          <t>"Il Pescatorello"</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -4436,62 +4391,62 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>c.190 cm</t>
+          <t>c.90 cm</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/b/b7/The_Broncho_Buster_MET_1986.81.2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/Gemito_-_Jeune_napolitain_1870.jpg/960px-Gemito_-_Jeune_napolitain_1870.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Frederic</t>
+          <t>Vincenzo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>REMINGTON</t>
+          <t>GEMITO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Fort Worth</t>
+          <t>palais Zevallos</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Amon Carter Museum of American Art</t>
+          <t>Naples</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>"Le Bronco Buster"</t>
+          <t>"Gamin napolitain"</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -4501,362 +4456,377 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>c.60 cm</t>
+          <t>c.90 cm</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/03/Giovanni_dupr%C3%A9%2C_abele_morente_01.jpg/1280px-Giovanni_dupr%C3%A9%2C_abele_morente_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7b/L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG/960px-L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Giovanni</t>
+          <t>Jean-Léon</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DUPRÉ</t>
+          <t>GÉRÔME</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1844-1951</t>
+          <t>1890</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Palazzo Pitti</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>"Abel mourant"</t>
+          <t>"Tanagra"</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Marbre polychrome et ivoire</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>c.170 cm</t>
+          <t>c.190 cm</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/7/74/Uffizi_Giotto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png/960px-John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Giovanni</t>
+          <t>John</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DUPRÉ</t>
+          <t>GIBSON</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1851-1856</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Piazzale des Offices</t>
+          <t>Walker Art Gallery</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>"Statue de Giotto"</t>
+          <t>"La Vénus teintée (Tinted Venus)"</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Marbre polychrome</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>c.175 cm</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/55/Statue_of_Gaspard_de_Coligny_%40_Paris_%2832269434936%29.jpg/960px-Statue_of_Gaspard_de_Coligny_%40_Paris_%2832269434936%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Piccadilly.jpg/960px-Piccadilly.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Gustave</t>
+          <t>Alfred</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CRAUK</t>
+          <t>GILBERT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Temple de l’Oratoire du Louvre</t>
+          <t>Piccadilly Circus</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>"Statue de Gaspard de Coligny"</t>
+          <t>"La Fontaine d'Éros"</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Bronze doré et aluminium</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/25/LeTemps_fauchant_les_amours.jpg/500px-LeTemps_fauchant_les_amours.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7d/%D0%92%D0%B0%D1%80%D1%88%D0%B0%D0%B2%D0%B0_-_panoramio_%28130%29.jpg/960px-%D0%92%D0%B0%D1%80%D1%88%D0%B0%D0%B2%D0%B0_-_panoramio_%28130%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Gustave</t>
+          <t>Cyprian</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DORÉ</t>
+          <t>GODEBSKI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1897-1898</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Varsovie</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Musée des Arts décoratifs de Paris</t>
+          <t>Krakowskie Przedmieście</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>"LeTemps fauchant les amours"</t>
+          <t>"Monument à Adam Mickiewicz"</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>c.180 cm</t>
+          <t>Bronze et pierre</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>polonaise</t>
         </is>
       </c>
       <c r="U68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/Monument_Dumas%2C_Paris%2C_16_April_2022.jpg/960px-Monument_Dumas%2C_Paris%2C_16_April_2022.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/49/Hosmer_-_Zenobia_in_Chains_-_front_view_-_HLAMBG.png/330px-Hosmer_-_Zenobia_in_Chains_-_front_view_-_HLAMBG.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Gustave</t>
+          <t>Harriet</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DORÉ</t>
+          <t>HOSMER</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1882-1883</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Hartford</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Place du Général Catroux</t>
+          <t>Wadsworth Atheneum</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>"Monument à Alexandre Dumas"</t>
+          <t>"Zenobia enchaînée"</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Bronze et pierre</t>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>c.140 cm</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Hamo_Thornycroft-Teucer-07211.jpg/960px-Hamo_Thornycroft-Teucer-07211.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/2/2e/Horseman_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hamo</t>
+          <t>Pyotr</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>THORNYCROFT</t>
+          <t>KLODT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1841-1850</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Saint-Pétersbourg</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Tate Britain</t>
+          <t>Pont Anitchkov</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>"Teucer"</t>
+          <t>"Les Chevaux dressés (groupe du pont Anitchkov)"</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -4864,129 +4834,114 @@
           <t>Bronze</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>c.220 cm</t>
-        </is>
-      </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>russe</t>
         </is>
       </c>
       <c r="U70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/49/Hosmer_-_Zenobia_in_Chains_-_front_view_-_HLAMBG.png/330px-Hosmer_-_Zenobia_in_Chains_-_front_view_-_HLAMBG.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg/1280px-RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Harriet</t>
+          <t>Pyotr</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HOSMER</t>
+          <t>KLODT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1859</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Hartford</t>
+          <t>1856-1859</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Wadsworth Atheneum</t>
+          <t>Place Saint-Isaac à Saint-Pétersbourg</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>"Zenobia enchaînée"</t>
+          <t>"Statue de l'empereur Nicolas Ier"</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>c.140 cm</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>russe</t>
         </is>
       </c>
       <c r="U71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d5/La_Jeunesse%2C_S3494%2801%29.jpg/960px-La_Jeunesse%2C_S3494%2801%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/75/J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg/1280px-J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Henri</t>
+          <t>Jef</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CHAPU</t>
+          <t>LAMBEAUX</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1886-1898</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Bruxelles</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Musée Carnavalet</t>
+          <t>Pavillon des Passions humaines, Parc du Cinquantenaire</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>"La Jeunesse"</t>
+          <t>"Les Passions humaines"</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -4994,194 +4949,189 @@
           <t>Marbre</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>c.150 cm</t>
-        </is>
-      </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>belge</t>
         </is>
       </c>
       <c r="U72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e5/Henri_Chapu_-_Jeanne_d%27Arc.jpg/960px-Henri_Chapu_-_Jeanne_d%27Arc.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9d/An_athlete_wrestling_a_python.png/960px-An_athlete_wrestling_a_python.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Henri</t>
+          <t>Frederic</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CHAPU</t>
+          <t>LEIGHTON</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Tate Britain</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>"Jeanne d’Arc à Domremy"</t>
+          <t>"Athlète luttant avec un python"</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>c.190 cm</t>
+          <t>c.175 cm</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG/960px-The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/7/7d/Frederic_Leighton_-_The_Sluggard_-_B1982.17_-_Yale_Center_for_British_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original&amp;uselang=fr</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hiram</t>
+          <t>Frederic</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>POWERS</t>
+          <t>LEIGHTON</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Université de Yale</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>National Gallery of Art</t>
+          <t>Yale Center for British Art</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>"L'Esclave grecque"</t>
+          <t>"Le Paresseux"</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>c.166 cm</t>
+          <t>c.190 cm</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg/960px-Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/89/Edmonia_Lewis_-_The_death_of_Cleopatra.jpg/960px-Edmonia_Lewis_-_The_death_of_Cleopatra.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Edmonia</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PRADIER</t>
+          <t>LEWIS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Smithsonian American Art Museum</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>"Sapho"</t>
+          <t>"La Mort de Cléopâtre"</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -5191,12 +5141,12 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>c.122 cm</t>
+          <t>c.160 cm</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>suisse</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U75" t="n">
@@ -5206,32 +5156,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/dd/Les_Trois_Graces_LP_5.jpg/960px-Les_Trois_Graces_LP_5.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/2/25/David-Antonin_Mercie-IMG_8380-white.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Antonin</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PRADIER</t>
+          <t>MERCIÉ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5241,27 +5191,27 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>"Les Trois Grâces"</t>
+          <t>"David"</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>c.172 cm</t>
+          <t>c.180 cm</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>suisse</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U76" t="n">
@@ -5271,32 +5221,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG/960px-Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8f/Gloria_Victis_-_Anthonin_Merci%C3%A9.jpg/960px-Gloria_Victis_-_Anthonin_Merci%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Jean-Baptiste</t>
+          <t>Antonin</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CARPEAUX</t>
+          <t>MERCIÉ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5306,17 +5256,22 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Musée du Petit Palais</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>"La Danse (façade de l'Opéra de Paris)"</t>
+          <t>"Gloria Victis"</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>c.280 cm</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -5331,47 +5286,47 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg/1280px-20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=lt</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f6/Belgique_-_Bruxelles_-_Botanique_-_L%27Automne_ou_Le_Semeur_de_Constantin_Meunier_-_01.jpg/960px-Belgique_-_Bruxelles_-_Botanique_-_L%27Automne_ou_Le_Semeur_de_Constantin_Meunier_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Jean-Baptiste</t>
+          <t>Constantin</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CARPEAUX</t>
+          <t>MEUNIER</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1892-1896</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Bruxelles</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Jardin des Grands Explorateurs (de l'Observatoire)</t>
+          <t>Jardin botanique</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>"Fontaine des Quatre-Parties-du-Monde"</t>
+          <t>"Le Semeur (L'Automne)"</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -5379,64 +5334,69 @@
           <t>Bronze</t>
         </is>
       </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>c.220 cm</t>
+        </is>
+      </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>belge</t>
         </is>
       </c>
       <c r="U78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1a/Ugolino_Carpeaux_Petit_Palais_PPSO1573.jpg/960px-Ugolino_Carpeaux_Petit_Palais_PPSO1573.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ad/Alise-Sainte-Reine_-_Statue_de_Vercing%C3%A9torix_-_01.jpg/960px-Alise-Sainte-Reine_-_Statue_de_Vercing%C3%A9torix_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Jean-Baptiste</t>
+          <t>Aimé</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CARPEAUX</t>
+          <t>MILLET</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1857-1861</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>site d'Alésia</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Petit Palais</t>
+          <t>Alise-Sainte-Reine</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>"Ugolin entouré de ses quatre enfants,"</t>
+          <t>"Statue de Vercingétorix"</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Cuivre repoussé</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -5445,38 +5405,38 @@
         </is>
       </c>
       <c r="U79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Sculpture-7808948_%2852096525415%29.jpg/1280px-Sculpture-7808948_%2852096525415%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/1/15/Apollon_opera_Garnier_n3.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Jean-Baptiste</t>
+          <t>Aimé</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CLÉSINGER</t>
+          <t>MILLET</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1860-1869</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5486,17 +5446,17 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Palais Garnier</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>"La Femme piquée par un serpent"</t>
+          <t>"Apollon, la Poésie et la Musique. Toit du Palais Garnier"</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Cuivre doré</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -5505,53 +5465,58 @@
         </is>
       </c>
       <c r="U80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/64/Chopin_Grave_Grab_Pere_Lachaise.JPG/960px-Chopin_Grave_Grab_Pere_Lachaise.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/f/f9/Mathurin_Moreau_Oceanie_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Jean-Baptiste</t>
+          <t>Mathurin</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CLÉSINGER</t>
+          <t>MOREAU</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Cimetière du Père-Lachaise à Paris</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>"Monument funéraire de Frédéric Chopin"</t>
+          <t>"L'Océanie"</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -5566,52 +5531,52 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/6/64/Paris_8e_-_Petit_Palais_-_Mus%C3%A9e_des_Beaux-Arts_-_Bacchante_%28Auguste_Cl%C3%A9singer%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/e/e2/FontaineDeTournyQuebec.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Jean-Baptiste</t>
+          <t>Mathurin</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CLÉSINGER</t>
+          <t>MOREAU</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>actuellement  Place de l’Assemblée-Nationale à Québec</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Petit Palais</t>
+          <t>Anciennement allée de Tourny à Bordeaux</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>"Bacchante couchée"</t>
+          <t>"Fontaine modèle "Tourny""</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Fonte de fer</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -5626,62 +5591,57 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7b/L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG/960px-L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/34/%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg/960px-%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jean-Léon</t>
+          <t>Josef Václav</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GÉRÔME</t>
+          <t>MYSLBEK</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1887-1924</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Prague</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Place Venceslas</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>"Tanagra"</t>
+          <t>"Monument équestre à saint Venceslas"</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Marbre polychrome et ivoire</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>c.190 cm</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>tchèque</t>
         </is>
       </c>
       <c r="U83" t="n">
@@ -5691,47 +5651,47 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/75/J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg/1280px-J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0b/Musee_D%27Orsay_%2814705374093%29.jpg/960px-Musee_D%27Orsay_%2814705374093%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jef</t>
+          <t>Jean-Joseph</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LAMBEAUX</t>
+          <t>PERRAUD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1886-1898</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Bruxelles</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Pavillon des Passions humaines, Parc du Cinquantenaire</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>"Les Passions humaines"</t>
+          <t>"Le Désespoir"</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -5739,69 +5699,74 @@
           <t>Marbre</t>
         </is>
       </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>c.90 cm</t>
+        </is>
+      </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>belge</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/d/d1/Restored_quadriga_atop_Brandenburg_Gate.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/82/Estatua_de_Miguel_de_Cervantes_%286_de_diciembre_de_2005%2C_Madrid%29_02.JPG/960px-Estatua_de_Miguel_de_Cervantes_%286_de_diciembre_de_2005%2C_Madrid%29_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Johann Gottfried</t>
+          <t>José</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SCHADOW</t>
+          <t>PIQUER Y DUART</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Porte de Brandebourg</t>
+          <t>Plaza de las Cortes</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>"Quadrige de la Porte de Brandebourg"</t>
+          <t>"Reliefs en bronze du monument à Cervantès (Don Quichotte et Sancho Pança)"</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Cuivre repoussé</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>espagnole</t>
         </is>
       </c>
       <c r="U85" t="n">
@@ -5811,62 +5776,62 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png/960px-John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG/960px-The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Hiram</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GIBSON</t>
+          <t>POWERS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1851-1856</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Walker Art Gallery</t>
+          <t>National Gallery of Art</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>"La Vénus teintée (Tinted Venus)"</t>
+          <t>"L'Esclave grecque"</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Marbre polychrome</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>c.175 cm</t>
+          <t>c.166 cm</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U86" t="n">
@@ -5876,152 +5841,162 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/82/Estatua_de_Miguel_de_Cervantes_%286_de_diciembre_de_2005%2C_Madrid%29_02.JPG/960px-Estatua_de_Miguel_de_Cervantes_%286_de_diciembre_de_2005%2C_Madrid%29_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg/960px-Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>José</t>
+          <t>James</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PIQUER Y DUART</t>
+          <t>PRADIER</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Plaza de las Cortes</t>
+          <t>Musée d'Orsay</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>"Reliefs en bronze du monument à Cervantès (Don Quichotte et Sancho Pança)"</t>
+          <t>"Sapho"</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>c.122 cm</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>espagnole</t>
+          <t>suisse</t>
         </is>
       </c>
       <c r="U87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/34/%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg/960px-%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/dd/Les_Trois_Graces_LP_5.jpg/960px-Les_Trois_Graces_LP_5.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Josef Václav</t>
+          <t>James</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MYSLBEK</t>
+          <t>PRADIER</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1887-1924</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Prague</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Place Venceslas</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>"Monument équestre à saint Venceslas"</t>
+          <t>"Les Trois Grâces"</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>c.172 cm</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>tchèque</t>
+          <t>suisse</t>
         </is>
       </c>
       <c r="U88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/57/Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg/960px-Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5f/Pr%C3%A9ault_-_Le_Silence_-_Robl%C3%A8s_01.jpg/960px-Pr%C3%A9ault_-_Le_Silence_-_Robl%C3%A8s_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>Auguste</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>DALOU</t>
+          <t>PRÉAULT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6031,12 +6006,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Place de la Nation</t>
+          <t>Cimetière du Père-Lachaise</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>"Le Triomphe de la République"</t>
+          <t>"Le Silence"</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -6044,59 +6019,64 @@
           <t>Bronze</t>
         </is>
       </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>c.40 cm</t>
+        </is>
+      </c>
       <c r="T89" t="inlineStr">
         <is>
           <t>française</t>
         </is>
       </c>
       <c r="U89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/47/Dalou_paysan.jpg/960px-Dalou_paysan.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/58/Berlin_Friedrich_II_Denkmal_09-2017_img1.jpg/960px-Berlin_Friedrich_II_Denkmal_09-2017_img1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>Christian Daniel</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DALOU</t>
+          <t>RAUCH</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1897-1902</t>
+          <t>1839-1851</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Unter den Linden</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>"Grand paysan"</t>
+          <t>"Monument équestre à Frédéric le Grand"</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -6104,84 +6084,74 @@
           <t>Bronze</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>c.100 cm</t>
-        </is>
-      </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ed/Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG/1280px-Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/b/b7/The_Broncho_Buster_MET_1986.81.2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Frederic</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BARTOLINI</t>
+          <t>REMINGTON</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1837-1845</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Fort Worth</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Amon Carter Museum of American Art</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>"Nymphe au scorpion"</t>
+          <t>"Le Bronco Buster"</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>80 cm</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>180 cm</t>
+          <t>c.60 cm</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U91" t="n">
@@ -6191,62 +6161,57 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/dd/Barrias_La_Nature_se_d%C3%A9voilant.jpg/1920px-Barrias_La_Nature_se_d%C3%A9voilant.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f0/Denkmal_-_panoramio_%2864%29.jpg/960px-Denkmal_-_panoramio_%2864%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Louis-Ernest</t>
+          <t>Ernst</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BARRIAS</t>
+          <t>RIETSCHEL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Weimar</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Theaterplatz</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>"La Nature se dévoilant à la Science"</t>
+          <t>"Monument à Goethe et Schiller"</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Marbre, onyx et bronze</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>c.200 cm</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U92" t="n">
@@ -6256,32 +6221,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c4/La_D%C3%A9fense_de_Paris_%40_Parvis_%40_La_D%C3%A9fense_%40_Paris_%2834342635104%29.jpg/1920px-La_D%C3%A9fense_de_Paris_%40_Parvis_%40_La_D%C3%A9fense_%40_Paris_%2834342635104%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Le_Penseur_Mus%C3%A9e_Rodin_Paris_S.1295.jpg/960px-Le_Penseur_Mus%C3%A9e_Rodin_Paris_S.1295.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Louis-Ernest</t>
+          <t>Auguste</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BARRIAS</t>
+          <t>RODIN</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1880-1904</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6291,12 +6256,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Rond-point de la Défense</t>
+          <t>Musée Rodin</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>"La Défense de Paris"</t>
+          <t>"Le Penseur"</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -6304,59 +6269,64 @@
           <t>Bronze</t>
         </is>
       </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>189 cm</t>
+        </is>
+      </c>
       <c r="T93" t="inlineStr">
         <is>
           <t>française</t>
         </is>
       </c>
       <c r="U93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Museo_Nacional_de_Arte_Mexico_DF%2C_Manuel_Vilarm_Tlahuicole_General_Tlaxcalteca_1851_%2822153403811%29.jpg/960px-Museo_Nacional_de_Arte_Mexico_DF%2C_Manuel_Vilarm_Tlahuicole_General_Tlaxcalteca_1851_%2822153403811%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/2018_Balzac_%281898%29_1.jpg/960px-2018_Balzac_%281898%29_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Auguste</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>VILAR</t>
+          <t>RODIN</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Museo Nacional de Arte</t>
+          <t>Musée Rodin</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>"Tlahuicole"</t>
+          <t>"Monument à Balzac"</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -6364,134 +6334,139 @@
           <t>Bronze</t>
         </is>
       </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>270 cm</t>
+        </is>
+      </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>espagnole</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/38/Socrates_dying_by_Mark_Antokolsky2.jpg/1280px-Socrates_dying_by_Mark_Antokolsky2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/04/Statue_bourgeois_calais_rodin.jpg/1280px-Statue_bourgeois_calais_rodin.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Auguste</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ANTOKOLSKY</t>
+          <t>RODIN</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1884-1895</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Saint-Pétersbourg</t>
+          <t>Calais</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Musée russe</t>
+          <t>Place de l’hôtel de ville</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>"Mort de Socrate"</t>
+          <t>"Les Bourgeois de Calais"</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>217 cm</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>russe</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/08/MAntokolski_IvanIV.JPG/960px-MAntokolski_IvanIV.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Rodin_-_Le_Baiser_06.jpg/960px-Rodin_-_Le_Baiser_06.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Auguste</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ANTOKOLSKY</t>
+          <t>RODIN</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1881-1882</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Saint-Pétersbourg</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Musée russe</t>
+          <t>Musée Rodin</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>"Ivan le terrible"</t>
+          <t>"Le Baiser"</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>c.200 cm</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>russe</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U96" t="n">
@@ -6501,47 +6476,47 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/a/a8/MAntokolsky_Mefisto.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/7/77/Rodin_The_bronze_age.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Auguste</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ANTOKOLSKY</t>
+          <t>RODIN</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Saint-Pétersbourg</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Musée russe</t>
+          <t>Alte Nationalgalerie</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>"Méphistophélès"</t>
+          <t>"L'Âge d'airain"</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -6551,12 +6526,12 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>c.60 cm</t>
+          <t>178 cm</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>russe</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U97" t="n">
@@ -6566,117 +6541,122 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/f/f9/Mathurin_Moreau_Oceanie_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Nydia_the_blind_flower_girl_1763.JPG/960px-Nydia_the_blind_flower_girl_1763.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mathurin</t>
+          <t>Randolph</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MOREAU</t>
+          <t>ROGERS</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>"L'Océanie"</t>
+          <t>"Nydia, la fleuriste aveugle de Pompéi"</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>c.140 cm</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/e/e2/FontaineDeTournyQuebec.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/77/Lincoln_1871_Fairmount.jpg/960px-Lincoln_1871_Fairmount.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Mathurin</t>
+          <t>Randolph</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MOREAU</t>
+          <t>ROGERS</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1870-1871</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>actuellement  Place de l’Assemblée-Nationale à Québec</t>
+          <t>Philadelphie</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Anciennement allée de Tourny à Bordeaux</t>
+          <t>East Fairmount Park</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>"Fontaine modèle "Tourny""</t>
+          <t>"Statue d’Abraham Lincoln assis signant la Proclamation d’émancipation"</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Fonte de fer</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U99" t="n">
@@ -6686,32 +6666,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b1/Paul_Dubois_Chanteur_florentin.jpg/960px-Paul_Dubois_Chanteur_florentin.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg/960px-Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>François</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DUBOIS</t>
+          <t>RUDE</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6721,22 +6701,17 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>Arc de Triomphe</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>"Le Chanteur florentin (Le Condottiere)"</t>
+          <t>"Le Départ des volontaires de 1792 (La Marseillaise)"</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>c.190 cm</t>
+          <t>Pierre</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
@@ -6745,63 +6720,63 @@
         </is>
       </c>
       <c r="U100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/3/32/Eve_naissante_Dubois_Petit_Palais_PPS00946.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/b/bb/Head_of_the_Old_Warrior_%28T%C3%AAte_du_Guerrier%29_MET_63761.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>François</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DUBOIS</t>
+          <t>RUDE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Petit Palais</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>"Ève naissante"</t>
+          <t>"Tête du Guerrier"</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>c.175 cm</t>
+          <t>c.40 cm</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
@@ -6816,52 +6791,57 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/Strasbourg_StMaurice_004.JPG/1280px-Strasbourg_StMaurice_004.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/e/e2/David_Rude_Louvre_LP1780.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>François</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>DUBOIS</t>
+          <t>RUDE</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Église catholique Saint-Maurice</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>"Statue équestre de Jeanne d’Arc"</t>
+          <t>"Buste du peintre français Jacques Louis David"</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bronze</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>c.60 cm</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -6876,52 +6856,52 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c0/PolyxenaFedi.jpg/960px-PolyxenaFedi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9d/Mus%C3%A9e_et_Parc_Noisot_005.jpg/1280px-Mus%C3%A9e_et_Parc_Noisot_005.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Pio</t>
+          <t>François</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FEDI</t>
+          <t>RUDE</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Fixin</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Loggia dei Lanzi</t>
+          <t>Parc Noiset</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>"L'Enlèvement de Polyxène"</t>
+          <t>"Napoléon s'éveillant à l'Immortalité"</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -6931,67 +6911,67 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Pio_fedi%2C_monumento_funebre_a_Giovan_Battista_Niccolini%2C_1883%2C_02_personificazione_della_libert%C3%A0_della_poesia.jpg/960px-Pio_fedi%2C_monumento_funebre_a_Giovan_Battista_Niccolini%2C_1883%2C_02_personificazione_della_libert%C3%A0_della_poesia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Baptism_of_Christ%2C_%C3%89glise_de_la_Madeleine%2C_Paris_July_2011.jpg/1280px-Baptism_of_Christ%2C_%C3%89glise_de_la_Madeleine%2C_Paris_July_2011.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Pio</t>
+          <t>François</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FEDI</t>
+          <t>RUDE</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Basilique Santa Croce</t>
+          <t>Église de la Madeleine</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>"La Liberté de la Poésie"</t>
+          <t>"Le Baptême du Christ"</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Pierre</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U104" t="n">
@@ -7001,102 +6981,112 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/2/2e/Horseman_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Art%26Archeologie_Valence063a_Fran%C3%A7ois_Rude.jpg/1280px-Art%26Archeologie_Valence063a_Fran%C3%A7ois_Rude.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Pyotr</t>
+          <t>François</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>KLODT</t>
+          <t>RUDE</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1841-1850</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Saint-Pétersbourg</t>
+          <t>Valence</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Pont Anitchkov</t>
+          <t>Musée d’art et d’archéologie</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>"Les Chevaux dressés (groupe du pont Anitchkov)"</t>
+          <t>"Jeune pêcheur napolitain jouant avec une tortue"</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>c.82 cm</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>russe</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg/1280px-RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG/1280px-Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Pyotr</t>
+          <t>Augustus</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>KLODT</t>
+          <t>SAINT-GAUDENS</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>1856-1859</t>
+          <t>1897</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Boston</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Place Saint-Isaac à Saint-Pétersbourg</t>
+          <t>Boston Common</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>"Statue de l'empereur Nicolas Ier"</t>
+          <t>"Monument à Robert Gould Shaw et au 54e régiment du Massachusetts"</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -7106,107 +7096,102 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>russe</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Nydia_the_blind_flower_girl_1763.JPG/960px-Nydia_the_blind_flower_girl_1763.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/d/d1/Restored_quadriga_atop_Brandenburg_Gate.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Randolph</t>
+          <t>Johann Gottfried</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ROGERS</t>
+          <t>SCHADOW</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art</t>
+          <t>Porte de Brandebourg</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>"Nydia, la fleuriste aveugle de Pompéi"</t>
+          <t>"Quadrige de la Porte de Brandebourg"</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>c.140 cm</t>
+          <t>Cuivre repoussé</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/77/Lincoln_1871_Fairmount.jpg/960px-Lincoln_1871_Fairmount.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Washington_Monument-Philadelphia-27527.jpg/1280px-Washington_Monument-Philadelphia-27527.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Randolph</t>
+          <t>Rudolf</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ROGERS</t>
+          <t>SIEMERING</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1870-1871</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7216,77 +7201,87 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>East Fairmount Park</t>
+          <t>Eakins Oval (autrefois Fairmount Park)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>"Statue d’Abraham Lincoln assis signant la Proclamation d’émancipation"</t>
+          <t>"Monument national à Washington"</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/69/Neptunbrunnen_Berlin_2.jpg/1280px-Neptunbrunnen_Berlin_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3e/Captive_Mother_by_Stephan_Sinding.jpg/1280px-Captive_Mother_by_Stephan_Sinding.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Reinhold</t>
+          <t>Stephan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BEGAS</t>
+          <t>SINDING</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1888</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Copenhague</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Ny Carlsberg Glyptotek</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>"Neptunbrunnen (Fontaine de Neptune)"</t>
+          <t>"Mère captive (Den fangne mor)"</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Bronze et marbre</t>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>c.130 cm</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>norvégienne</t>
         </is>
       </c>
       <c r="U109" t="n">
@@ -7296,52 +7291,57 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/73/Schillerdenkmal_Berlin_Gendarmenmarkt_Begas_1.jpg/960px-Schillerdenkmal_Berlin_Gendarmenmarkt_Begas_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/86/Cathedral_Church_of_St_Paul%2C_Monument_to_the_1st_Duke_of_Wellington_City_of_London_1079157_20230822_0197.jpg/960px-Cathedral_Church_of_St_Paul%2C_Monument_to_the_1st_Duke_of_Wellington_City_of_London_1079157_20230822_0197.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Reinhold</t>
+          <t>Alfred</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BEGAS</t>
+          <t>STEVENS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1862-1871</t>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Gendarmenmarkt à Berlin</t>
+          <t>Cathédrale Saint-Paul</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>"Mémorial Schiller"</t>
+          <t>"Monument au duc de Wellington"</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Bronze et marbre</t>
+          <t>Marbre et bronze</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U110" t="n">
@@ -7351,57 +7351,62 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Washington_Monument-Philadelphia-27527.jpg/1280px-Washington_Monument-Philadelphia-27527.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/06/Cleopatra_by_William_Wetmore_Story_01.jpg/1280px-Cleopatra_by_William_Wetmore_Story_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Rudolf</t>
+          <t>William Wetmore</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SIEMERING</t>
+          <t>STORY</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1858-1869</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Philadelphie</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Eakins Oval (autrefois Fairmount Park)</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>"Monument national à Washington"</t>
+          <t>"Cléopâtre"</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>c.160 cm</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U111" t="n">
@@ -7411,47 +7416,42 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3e/Captive_Mother_by_Stephan_Sinding.jpg/1280px-Captive_Mother_by_Stephan_Sinding.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/f/f2/Emelyn_Story_Tomba_%28Cimitero_Acattolico_Roma%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Stephan</t>
+          <t>William Wetmore</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SINDING</t>
+          <t>STORY</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1888</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>Copenhague</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Ny Carlsberg Glyptotek</t>
+          <t>Cimetière protestant de Rome</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>"Mère captive (Den fangne mor)"</t>
+          <t>"Angel of grief, pierre tombale de l’artiste et de son épouse Emelyn"</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -7461,16 +7461,16 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>c.130 cm</t>
+          <t>c.210 cm</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>norvégienne</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -7536,47 +7536,47 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/b/b4/Emancipation_memorial_MRD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Hamo_Thornycroft-Teucer-07211.jpg/960px-Hamo_Thornycroft-Teucer-07211.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Hamo</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BALL</t>
+          <t>THORNYCROFT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Lincoln Park</t>
+          <t>Tate Britain</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>"Monument à l'émancipation (Emancipation Memorial)"</t>
+          <t>"Teucer"</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -7584,139 +7584,144 @@
           <t>Bronze</t>
         </is>
       </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>c.220 cm</t>
+        </is>
+      </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/9/94/The_Fisher_Boy_by_Vincenzo_Gemito%2C_Museo_del_Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/Vor_Frue_Kirke_Copenhagen_altar.jpg/960px-Vor_Frue_Kirke_Copenhagen_altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Vincenzo</t>
+          <t>Bertel</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GEMITO</t>
+          <t>THORVALDSEN</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Copenhague</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Museo Nazionale del Bargello</t>
+          <t>Cathédrale Notre-Dame (Vor Frue Kirke)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>"Il Pescatorello"</t>
+          <t>"Le Christ"</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>c.90 cm</t>
+          <t>c.275 cm</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>danoise</t>
         </is>
       </c>
       <c r="U115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/Gemito_-_Jeune_napolitain_1870.jpg/960px-Gemito_-_Jeune_napolitain_1870.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Jas%C3%A3o_e_o_Velo_de_ouro_-_Bertel_Thorvaldsen_-_1803.jpg/960px-Jas%C3%A3o_e_o_Velo_de_ouro_-_Bertel_Thorvaldsen_-_1803.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Vincenzo</t>
+          <t>Bertel</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GEMITO</t>
+          <t>THORVALDSEN</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>palais Zevallos</t>
+          <t>Copenhague</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Musée Thorvaldsen</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>"Gamin napolitain"</t>
+          <t>"Jason à la Toison d'or"</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>c.90 cm</t>
+          <t>242 cm</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>danoise</t>
         </is>
       </c>
       <c r="U116" t="n">
@@ -7781,62 +7786,57 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/06/Cleopatra_by_William_Wetmore_Story_01.jpg/1280px-Cleopatra_by_William_Wetmore_Story_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Museo_Nacional_de_Arte_Mexico_DF%2C_Manuel_Vilarm_Tlahuicole_General_Tlaxcalteca_1851_%2822153403811%29.jpg/960px-Museo_Nacional_de_Arte_Mexico_DF%2C_Manuel_Vilarm_Tlahuicole_General_Tlaxcalteca_1851_%2822153403811%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>William Wetmore</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>STORY</t>
+          <t>VILAR</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1858-1869</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art</t>
+          <t>Museo Nacional de Arte</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>"Cléopâtre"</t>
+          <t>"Tlahuicole"</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>c.160 cm</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>espagnole</t>
         </is>
       </c>
       <c r="U118" t="n">
@@ -7846,102 +7846,107 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/f/f2/Emelyn_Story_Tomba_%28Cimitero_Acattolico_Roma%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/f/f5/Fountain_On_Lenbachplatz_-_panoramio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=de</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>William Wetmore</t>
+          <t>Adolf</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>STORY</t>
+          <t>von HILDEBRAND</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1893-1895</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Munich</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Cimetière protestant de Rome</t>
+          <t>Lenbachplatz</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>"Angel of grief, pierre tombale de l’artiste et de son épouse Emelyn"</t>
+          <t>"Fontaine Wittelsbach (Wittelsbacherbrunnen)"</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>c.210 cm</t>
+          <t>Pierre et bronze</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Chaire_Cath%C3%A9drale_Li%C3%A8ge_240809_03.jpg/960px-Chaire_Cath%C3%A9drale_Li%C3%A8ge_240809_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8b/Hirtenknabe.jpg/960px-Hirtenknabe.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Guillaume</t>
+          <t>Adolf</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>GEEFS</t>
+          <t>von HILDEBRAND</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1871-1873</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Cathédrale de Liège</t>
+          <t>Alte Nationalgalerie</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>"Le Génie du Mal"</t>
+          <t>"Jeune pâtre endormi"</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -7951,12 +7956,12 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>c.220 cm</t>
+          <t>c.90 cm</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>belge</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U120" t="n">
@@ -7966,47 +7971,47 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0b/Musee_D%27Orsay_%2814705374093%29.jpg/960px-Musee_D%27Orsay_%2814705374093%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5a/U.S._Capitol_Samuel_Adams_Statue.jpg/960px-U.S._Capitol_Samuel_Adams_Statue.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Jean-Joseph</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PERRAUD</t>
+          <t>WHITNEY</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
           <t>1876</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>1869</t>
-        </is>
-      </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Musée d'Orsay</t>
+          <t>United States Capitol</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>"Le Désespoir"</t>
+          <t>"Samuel Adams"</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -8014,18 +8019,13 @@
           <t>Marbre</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>c.90 cm</t>
-        </is>
-      </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/quizzes/sculpture-19e.xlsx
+++ b/quizzes/sculpture-19e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE49A223-521A-489E-840B-3E5EF86CB240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DCB747-1E0E-437E-94A8-9CC20FFB2E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="747">
   <si>
     <t>Prénom</t>
   </si>
@@ -469,9 +469,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Theseus_and_Centaur_by_Antonio_Canova_1.jpg/1280px-Theseus_and_Centaur_by_Antonio_Canova_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>340 cm environ</t>
-  </si>
-  <si>
     <t>Bakewell</t>
   </si>
   <si>
@@ -2177,13 +2174,100 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5a/U.S._Capitol_Samuel_Adams_Statue.jpg/960px-U.S._Capitol_Samuel_Adams_Statue.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>133 cm</t>
+  </si>
+  <si>
+    <t>125 cm</t>
+  </si>
+  <si>
+    <t>95 cm</t>
+  </si>
+  <si>
+    <t>366 cm (statue) 366 cm (piédestal)</t>
+  </si>
+  <si>
+    <t>550 cm</t>
+  </si>
+  <si>
+    <t>1056 cm</t>
+  </si>
+  <si>
+    <t>1906 cm</t>
+  </si>
+  <si>
+    <t>4600 cm (statue) 4700 cm (piédestal)</t>
+  </si>
+  <si>
+    <t>295 cm (statue) 200 cm (piédestal et allégories)</t>
+  </si>
+  <si>
+    <t>1000 cm</t>
+  </si>
+  <si>
+    <t>1800 cm (diamètre)</t>
+  </si>
+  <si>
+    <t>195 cm</t>
+  </si>
+  <si>
+    <t>150 cm</t>
+  </si>
+  <si>
+    <t>110 cm</t>
+  </si>
+  <si>
+    <t>Plâtre patiné</t>
+  </si>
+  <si>
+    <t>194 cm</t>
+  </si>
+  <si>
+    <t>148 cm</t>
+  </si>
+  <si>
+    <t>119 cm</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Jean-baptiste_carpeaux%2C_ugolino%2C_1862%2C_01.JPG/960px-Jean-baptiste_carpeaux%2C_ugolino%2C_1862%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>197,5 cm</t>
+  </si>
+  <si>
+    <t>149,9cm</t>
+  </si>
+  <si>
+    <t>110,5 cm</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Ugolino_and_His_Sons_MET_DP247545.jpg/960px-Ugolino_and_His_Sons_MET_DP247545.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>360 cm environ</t>
+  </si>
+  <si>
+    <t>375 cm</t>
+  </si>
+  <si>
+    <t>141 cm</t>
+  </si>
+  <si>
+    <t>146 cm environ</t>
+  </si>
+  <si>
+    <t>79cm environ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 cm environ </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2191,8 +2275,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2202,6 +2294,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2215,14 +2313,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2523,7 +2634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X121"/>
+  <dimension ref="A1:X123"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2544,8 +2655,8 @@
     <col min="16" max="16" width="17.140625" customWidth="1"/>
     <col min="17" max="17" width="11.85546875" customWidth="1"/>
     <col min="18" max="18" width="7.5703125" customWidth="1"/>
-    <col min="19" max="19" width="9.140625" customWidth="1"/>
-    <col min="20" max="20" width="7.140625" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="7.140625" style="3" customWidth="1"/>
     <col min="21" max="21" width="7" customWidth="1"/>
     <col min="22" max="22" width="3.28515625" customWidth="1"/>
     <col min="23" max="23" width="4.7109375" customWidth="1"/>
@@ -2607,10 +2718,10 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
       <c r="U1" t="s">
@@ -2654,10 +2765,10 @@
       <c r="N2" t="s">
         <v>32</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="3" t="s">
         <v>34</v>
       </c>
       <c r="W2" t="s">
@@ -2667,41 +2778,50 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="W3" t="s">
+      <c r="T3" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="W3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="X3">
+      <c r="X3" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2733,10 +2853,10 @@
       <c r="N4" t="s">
         <v>42</v>
       </c>
-      <c r="S4" t="s">
+      <c r="S4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="T4" t="s">
+      <c r="T4" s="3" t="s">
         <v>43</v>
       </c>
       <c r="W4" t="s">
@@ -2774,8 +2894,11 @@
       <c r="N5" t="s">
         <v>52</v>
       </c>
-      <c r="S5" t="s">
+      <c r="S5" s="3" t="s">
         <v>33</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>721</v>
       </c>
       <c r="W5" t="s">
         <v>53</v>
@@ -2812,8 +2935,11 @@
       <c r="N6" t="s">
         <v>62</v>
       </c>
-      <c r="S6" t="s">
+      <c r="S6" s="3" t="s">
         <v>33</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>722</v>
       </c>
       <c r="W6" t="s">
         <v>63</v>
@@ -2850,10 +2976,10 @@
       <c r="N7" t="s">
         <v>67</v>
       </c>
-      <c r="S7" t="s">
+      <c r="S7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="T7" t="s">
+      <c r="T7" s="3" t="s">
         <v>34</v>
       </c>
       <c r="W7" t="s">
@@ -2888,8 +3014,14 @@
       <c r="N8" t="s">
         <v>76</v>
       </c>
-      <c r="S8" t="s">
+      <c r="S8" s="3" t="s">
         <v>77</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="U8" t="s">
+        <v>724</v>
       </c>
       <c r="W8" t="s">
         <v>63</v>
@@ -2923,8 +3055,11 @@
       <c r="N9" t="s">
         <v>81</v>
       </c>
-      <c r="S9" t="s">
+      <c r="S9" s="3" t="s">
         <v>82</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>725</v>
       </c>
       <c r="W9" t="s">
         <v>63</v>
@@ -2961,10 +3096,10 @@
       <c r="N10" t="s">
         <v>90</v>
       </c>
-      <c r="S10" t="s">
+      <c r="S10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T10" t="s">
+      <c r="T10" s="3" t="s">
         <v>91</v>
       </c>
       <c r="U10" t="s">
@@ -3005,10 +3140,10 @@
       <c r="N11" t="s">
         <v>99</v>
       </c>
-      <c r="S11" t="s">
+      <c r="S11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="T11" t="s">
+      <c r="T11" s="3" t="s">
         <v>100</v>
       </c>
       <c r="U11" t="s">
@@ -3046,10 +3181,10 @@
       <c r="N12" t="s">
         <v>104</v>
       </c>
-      <c r="S12" t="s">
+      <c r="S12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="T12" t="s">
+      <c r="T12" s="3" t="s">
         <v>105</v>
       </c>
       <c r="W12" t="s">
@@ -3059,7 +3194,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>106</v>
       </c>
@@ -3084,8 +3219,11 @@
       <c r="N13" t="s">
         <v>112</v>
       </c>
-      <c r="S13" t="s">
+      <c r="S13" s="3" t="s">
         <v>113</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>726</v>
       </c>
       <c r="W13" t="s">
         <v>114</v>
@@ -3119,8 +3257,14 @@
       <c r="N14" t="s">
         <v>118</v>
       </c>
-      <c r="S14" t="s">
+      <c r="S14" s="3" t="s">
         <v>113</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="U14" t="s">
+        <v>728</v>
       </c>
       <c r="W14" t="s">
         <v>114</v>
@@ -3157,10 +3301,10 @@
       <c r="N15" t="s">
         <v>125</v>
       </c>
-      <c r="S15" t="s">
+      <c r="S15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T15" t="s">
+      <c r="T15" s="3" t="s">
         <v>126</v>
       </c>
       <c r="W15" t="s">
@@ -3170,126 +3314,144 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="M16" t="s">
+      <c r="M16" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="N16" t="s">
+      <c r="N16" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="S16" t="s">
+      <c r="S16" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="T16" t="s">
-        <v>134</v>
-      </c>
-      <c r="W16" t="s">
+      <c r="T16" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="W16" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="X16">
+      <c r="X16" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="17" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="M17" t="s">
+      <c r="M17" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="N17" t="s">
+      <c r="N17" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="S17" t="s">
+      <c r="S17" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="T17" t="s">
+      <c r="T17" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="W17" t="s">
+      <c r="U17" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="W17" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="X17">
+      <c r="X17" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="18" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="M18" t="s">
+      <c r="M18" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="N18" t="s">
+      <c r="N18" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="S18" t="s">
+      <c r="S18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="T18" t="s">
-        <v>149</v>
-      </c>
-      <c r="W18" t="s">
+      <c r="T18" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="W18" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="X18">
+      <c r="X18" s="2">
         <v>3</v>
       </c>
     </row>
@@ -3310,22 +3472,22 @@
         <v>143</v>
       </c>
       <c r="I19" t="s">
+        <v>149</v>
+      </c>
+      <c r="J19" t="s">
         <v>150</v>
       </c>
-      <c r="J19" t="s">
+      <c r="M19" t="s">
         <v>151</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>152</v>
       </c>
-      <c r="N19" t="s">
+      <c r="S19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T19" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="S19" t="s">
-        <v>39</v>
-      </c>
-      <c r="T19" t="s">
-        <v>154</v>
       </c>
       <c r="W19" t="s">
         <v>93</v>
@@ -3334,59 +3496,68 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="20" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B20" t="s">
+      <c r="F20" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G20" t="s">
-        <v>36</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="I20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="I20" t="s">
-        <v>59</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="M20" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="N20" t="s">
-        <v>161</v>
-      </c>
-      <c r="S20" t="s">
-        <v>33</v>
-      </c>
-      <c r="W20" t="s">
+      <c r="S20" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="T20" s="5" t="s">
+        <v>729</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="W20" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="X20">
+      <c r="X20" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>154</v>
+      </c>
+      <c r="B21" t="s">
         <v>155</v>
       </c>
-      <c r="B21" t="s">
+      <c r="F21" t="s">
         <v>156</v>
-      </c>
-      <c r="F21" t="s">
-        <v>157</v>
       </c>
       <c r="G21" t="s">
         <v>36</v>
       </c>
       <c r="H21" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I21" t="s">
         <v>59</v>
@@ -3395,51 +3566,69 @@
         <v>65</v>
       </c>
       <c r="M21" t="s">
-        <v>163</v>
-      </c>
-      <c r="N21" t="s">
-        <v>164</v>
-      </c>
-      <c r="S21" t="s">
-        <v>165</v>
+        <v>159</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="U21" t="s">
+        <v>734</v>
+      </c>
+      <c r="V21" t="s">
+        <v>735</v>
       </c>
       <c r="W21" t="s">
         <v>63</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>154</v>
+      </c>
+      <c r="B22" t="s">
         <v>155</v>
       </c>
-      <c r="B22" t="s">
+      <c r="F22" t="s">
         <v>156</v>
-      </c>
-      <c r="F22" t="s">
-        <v>157</v>
       </c>
       <c r="G22" t="s">
         <v>36</v>
       </c>
       <c r="H22" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="I22" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="J22" t="s">
-        <v>167</v>
+        <v>588</v>
       </c>
       <c r="M22" t="s">
-        <v>168</v>
-      </c>
-      <c r="N22" t="s">
-        <v>169</v>
-      </c>
-      <c r="S22" t="s">
-        <v>33</v>
+        <v>159</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="U22" t="s">
+        <v>738</v>
+      </c>
+      <c r="V22" t="s">
+        <v>739</v>
       </c>
       <c r="W22" t="s">
         <v>63</v>
@@ -3450,19 +3639,19 @@
     </row>
     <row r="23" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="B23" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="F23" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="G23" t="s">
-        <v>173</v>
+        <v>36</v>
       </c>
       <c r="H23" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="I23" t="s">
         <v>59</v>
@@ -3471,16 +3660,22 @@
         <v>65</v>
       </c>
       <c r="M23" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="N23" t="s">
-        <v>176</v>
-      </c>
-      <c r="S23" t="s">
-        <v>39</v>
-      </c>
-      <c r="T23" t="s">
-        <v>177</v>
+        <v>163</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="U23" t="s">
+        <v>734</v>
+      </c>
+      <c r="V23" t="s">
+        <v>735</v>
       </c>
       <c r="W23" t="s">
         <v>63</v>
@@ -3491,37 +3686,34 @@
     </row>
     <row r="24" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="F24" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="G24" t="s">
-        <v>173</v>
+        <v>36</v>
       </c>
       <c r="H24" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="I24" t="s">
         <v>59</v>
       </c>
       <c r="J24" t="s">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="M24" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="N24" t="s">
-        <v>180</v>
-      </c>
-      <c r="S24" t="s">
-        <v>39</v>
-      </c>
-      <c r="T24" t="s">
-        <v>43</v>
+        <v>168</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="W24" t="s">
         <v>63</v>
@@ -3532,72 +3724,81 @@
     </row>
     <row r="25" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>169</v>
+      </c>
+      <c r="B25" t="s">
         <v>170</v>
       </c>
-      <c r="B25" t="s">
+      <c r="F25" t="s">
         <v>171</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>172</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>173</v>
-      </c>
-      <c r="H25" t="s">
-        <v>181</v>
       </c>
       <c r="I25" t="s">
         <v>59</v>
       </c>
       <c r="J25" t="s">
-        <v>182</v>
+        <v>65</v>
       </c>
       <c r="M25" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="N25" t="s">
-        <v>184</v>
-      </c>
-      <c r="S25" t="s">
-        <v>185</v>
+        <v>175</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="W25" t="s">
         <v>63</v>
       </c>
       <c r="X25">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="B26" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="F26" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="G26" t="s">
-        <v>56</v>
+        <v>172</v>
       </c>
       <c r="H26" t="s">
-        <v>189</v>
+        <v>177</v>
+      </c>
+      <c r="I26" t="s">
+        <v>59</v>
       </c>
       <c r="J26" t="s">
-        <v>190</v>
+        <v>65</v>
       </c>
       <c r="M26" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="N26" t="s">
-        <v>192</v>
-      </c>
-      <c r="S26" t="s">
+        <v>179</v>
+      </c>
+      <c r="S26" s="3" t="s">
         <v>39</v>
       </c>
+      <c r="T26" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="W26" t="s">
-        <v>193</v>
+        <v>63</v>
       </c>
       <c r="X26">
         <v>3</v>
@@ -3605,37 +3806,34 @@
     </row>
     <row r="27" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="B27" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="F27" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="G27" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="H27" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="I27" t="s">
         <v>59</v>
       </c>
       <c r="J27" t="s">
-        <v>65</v>
+        <v>181</v>
       </c>
       <c r="M27" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="N27" t="s">
-        <v>199</v>
-      </c>
-      <c r="S27" t="s">
-        <v>39</v>
-      </c>
-      <c r="T27" t="s">
-        <v>134</v>
+        <v>183</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="W27" t="s">
         <v>63</v>
@@ -3646,60 +3844,54 @@
     </row>
     <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="B28" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F28" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="G28" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="H28" t="s">
-        <v>36</v>
-      </c>
-      <c r="I28" t="s">
-        <v>59</v>
+        <v>188</v>
       </c>
       <c r="J28" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="M28" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="N28" t="s">
-        <v>202</v>
-      </c>
-      <c r="S28" t="s">
+        <v>191</v>
+      </c>
+      <c r="S28" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T28" t="s">
-        <v>126</v>
-      </c>
       <c r="W28" t="s">
-        <v>63</v>
+        <v>192</v>
       </c>
       <c r="X28">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="B29" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="F29" t="s">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="G29" t="s">
-        <v>205</v>
+        <v>115</v>
       </c>
       <c r="H29" t="s">
-        <v>48</v>
+        <v>196</v>
       </c>
       <c r="I29" t="s">
         <v>59</v>
@@ -3708,212 +3900,218 @@
         <v>65</v>
       </c>
       <c r="M29" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="N29" t="s">
-        <v>207</v>
-      </c>
-      <c r="S29" t="s">
+        <v>198</v>
+      </c>
+      <c r="S29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T29" t="s">
+      <c r="T29" s="3" t="s">
         <v>134</v>
       </c>
       <c r="W29" t="s">
         <v>63</v>
       </c>
       <c r="X29">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="B30" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="F30" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G30" t="s">
-        <v>211</v>
+        <v>115</v>
       </c>
       <c r="H30" t="s">
-        <v>212</v>
+        <v>36</v>
       </c>
       <c r="I30" t="s">
         <v>59</v>
       </c>
       <c r="J30" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="M30" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="N30" t="s">
-        <v>215</v>
-      </c>
-      <c r="S30" t="s">
-        <v>33</v>
-      </c>
-      <c r="T30" t="s">
-        <v>177</v>
+        <v>201</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="W30" t="s">
         <v>63</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B31" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F31" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="G31" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="H31" t="s">
-        <v>216</v>
+        <v>48</v>
       </c>
       <c r="I31" t="s">
         <v>59</v>
       </c>
       <c r="J31" t="s">
-        <v>213</v>
+        <v>65</v>
       </c>
       <c r="M31" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="N31" t="s">
-        <v>218</v>
-      </c>
-      <c r="S31" t="s">
-        <v>219</v>
-      </c>
-      <c r="T31" t="s">
-        <v>220</v>
+        <v>206</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="W31" t="s">
         <v>63</v>
       </c>
       <c r="X31">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>207</v>
+      </c>
+      <c r="B32" t="s">
         <v>208</v>
       </c>
-      <c r="B32" t="s">
+      <c r="F32" t="s">
         <v>209</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>210</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>211</v>
-      </c>
-      <c r="H32" t="s">
-        <v>64</v>
       </c>
       <c r="I32" t="s">
         <v>59</v>
       </c>
       <c r="J32" t="s">
+        <v>212</v>
+      </c>
+      <c r="M32" t="s">
         <v>213</v>
       </c>
-      <c r="M32" t="s">
-        <v>221</v>
-      </c>
       <c r="N32" t="s">
-        <v>222</v>
-      </c>
-      <c r="S32" t="s">
+        <v>214</v>
+      </c>
+      <c r="S32" s="3" t="s">
         <v>33</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="W32" t="s">
         <v>63</v>
       </c>
       <c r="X32">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>155</v>
+        <v>207</v>
       </c>
       <c r="B33" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F33" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="G33" t="s">
-        <v>58</v>
+        <v>210</v>
       </c>
       <c r="H33" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="I33" t="s">
         <v>59</v>
       </c>
       <c r="J33" t="s">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="M33" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="N33" t="s">
-        <v>227</v>
-      </c>
-      <c r="S33" t="s">
-        <v>39</v>
+        <v>217</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>219</v>
       </c>
       <c r="W33" t="s">
         <v>63</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>155</v>
+        <v>207</v>
       </c>
       <c r="B34" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F34" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="G34" t="s">
-        <v>58</v>
+        <v>210</v>
       </c>
       <c r="H34" t="s">
-        <v>228</v>
+        <v>64</v>
       </c>
       <c r="I34" t="s">
         <v>59</v>
       </c>
       <c r="J34" t="s">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="M34" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="N34" t="s">
-        <v>230</v>
-      </c>
-      <c r="S34" t="s">
-        <v>39</v>
+        <v>221</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="W34" t="s">
         <v>63</v>
@@ -3924,157 +4122,151 @@
     </row>
     <row r="35" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B35" t="s">
+        <v>222</v>
+      </c>
+      <c r="F35" t="s">
         <v>223</v>
-      </c>
-      <c r="F35" t="s">
-        <v>224</v>
       </c>
       <c r="G35" t="s">
         <v>58</v>
       </c>
       <c r="H35" t="s">
-        <v>86</v>
+        <v>224</v>
+      </c>
+      <c r="I35" t="s">
+        <v>59</v>
       </c>
       <c r="J35" t="s">
-        <v>231</v>
+        <v>65</v>
       </c>
       <c r="M35" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="N35" t="s">
-        <v>233</v>
-      </c>
-      <c r="S35" t="s">
+        <v>226</v>
+      </c>
+      <c r="S35" s="3" t="s">
         <v>39</v>
       </c>
       <c r="W35" t="s">
         <v>63</v>
       </c>
       <c r="X35">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>234</v>
+        <v>154</v>
       </c>
       <c r="B36" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="F36" t="s">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="G36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H36" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="I36" t="s">
         <v>59</v>
       </c>
       <c r="J36" t="s">
-        <v>65</v>
+        <v>158</v>
       </c>
       <c r="M36" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="N36" t="s">
-        <v>238</v>
-      </c>
-      <c r="S36" t="s">
-        <v>239</v>
-      </c>
-      <c r="T36" t="s">
-        <v>177</v>
+        <v>229</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="W36" t="s">
         <v>63</v>
       </c>
       <c r="X36">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>240</v>
+        <v>154</v>
       </c>
       <c r="B37" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="F37" t="s">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="G37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H37" t="s">
-        <v>162</v>
-      </c>
-      <c r="I37" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="J37" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="M37" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="N37" t="s">
-        <v>244</v>
-      </c>
-      <c r="S37" t="s">
-        <v>33</v>
+        <v>232</v>
+      </c>
+      <c r="S37" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="W37" t="s">
         <v>63</v>
       </c>
       <c r="X37">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B38" t="s">
-        <v>246</v>
-      </c>
-      <c r="D38" t="s">
-        <v>247</v>
-      </c>
-      <c r="E38" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="F38" t="s">
-        <v>248</v>
+        <v>156</v>
       </c>
       <c r="G38" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="H38" t="s">
-        <v>249</v>
+        <v>235</v>
+      </c>
+      <c r="I38" t="s">
+        <v>59</v>
       </c>
       <c r="J38" t="s">
-        <v>250</v>
+        <v>65</v>
       </c>
       <c r="M38" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="N38" t="s">
-        <v>252</v>
-      </c>
-      <c r="S38" t="s">
-        <v>39</v>
-      </c>
-      <c r="T38" t="s">
-        <v>34</v>
+        <v>237</v>
+      </c>
+      <c r="S38" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="T38" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="W38" t="s">
-        <v>253</v>
+        <v>63</v>
       </c>
       <c r="X38">
         <v>2</v>
@@ -4082,292 +4274,295 @@
     </row>
     <row r="39" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="B39" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="F39" t="s">
-        <v>256</v>
+        <v>156</v>
       </c>
       <c r="G39" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="H39" t="s">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="I39" t="s">
         <v>59</v>
       </c>
       <c r="J39" t="s">
-        <v>65</v>
+        <v>241</v>
       </c>
       <c r="M39" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="N39" t="s">
-        <v>259</v>
-      </c>
-      <c r="S39" t="s">
+        <v>243</v>
+      </c>
+      <c r="S39" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="T39" t="s">
-        <v>260</v>
       </c>
       <c r="W39" t="s">
         <v>63</v>
       </c>
       <c r="X39">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="B40" t="s">
-        <v>255</v>
+        <v>245</v>
+      </c>
+      <c r="D40" t="s">
+        <v>246</v>
+      </c>
+      <c r="E40" t="s">
+        <v>246</v>
       </c>
       <c r="F40" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="G40" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="H40" t="s">
-        <v>64</v>
-      </c>
-      <c r="I40" t="s">
-        <v>59</v>
+        <v>248</v>
       </c>
       <c r="J40" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="M40" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="N40" t="s">
-        <v>263</v>
-      </c>
-      <c r="S40" t="s">
-        <v>33</v>
+        <v>251</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T40" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="W40" t="s">
-        <v>63</v>
+        <v>252</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="B41" t="s">
-        <v>265</v>
-      </c>
-      <c r="D41" t="s">
-        <v>266</v>
-      </c>
-      <c r="E41" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="F41" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="G41" t="s">
-        <v>268</v>
+        <v>27</v>
       </c>
       <c r="H41" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="I41" t="s">
         <v>59</v>
       </c>
       <c r="J41" t="s">
-        <v>270</v>
+        <v>65</v>
       </c>
       <c r="M41" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="N41" t="s">
-        <v>272</v>
-      </c>
-      <c r="S41" t="s">
-        <v>165</v>
+        <v>258</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>259</v>
       </c>
       <c r="W41" t="s">
         <v>63</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="B42" t="s">
-        <v>265</v>
-      </c>
-      <c r="D42" t="s">
-        <v>266</v>
-      </c>
-      <c r="E42" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="F42" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="G42" t="s">
-        <v>268</v>
+        <v>27</v>
       </c>
       <c r="H42" t="s">
-        <v>269</v>
+        <v>64</v>
       </c>
       <c r="I42" t="s">
         <v>59</v>
       </c>
       <c r="J42" t="s">
-        <v>88</v>
+        <v>260</v>
       </c>
       <c r="M42" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="N42" t="s">
-        <v>274</v>
-      </c>
-      <c r="S42" t="s">
+        <v>262</v>
+      </c>
+      <c r="S42" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="T42" t="s">
-        <v>275</v>
       </c>
       <c r="W42" t="s">
         <v>63</v>
       </c>
       <c r="X42">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>263</v>
+      </c>
+      <c r="B43" t="s">
         <v>264</v>
       </c>
-      <c r="B43" t="s">
+      <c r="D43" t="s">
         <v>265</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
+        <v>265</v>
+      </c>
+      <c r="F43" t="s">
         <v>266</v>
       </c>
-      <c r="E43" t="s">
-        <v>266</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>267</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>268</v>
       </c>
-      <c r="H43" t="s">
-        <v>276</v>
-      </c>
       <c r="I43" t="s">
-        <v>277</v>
+        <v>59</v>
       </c>
       <c r="J43" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="M43" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="N43" t="s">
-        <v>280</v>
-      </c>
-      <c r="S43" t="s">
-        <v>39</v>
-      </c>
-      <c r="T43" t="s">
-        <v>43</v>
+        <v>271</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="W43" t="s">
         <v>63</v>
       </c>
       <c r="X43">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="B44" t="s">
-        <v>282</v>
+        <v>264</v>
+      </c>
+      <c r="D44" t="s">
+        <v>265</v>
+      </c>
+      <c r="E44" t="s">
+        <v>265</v>
       </c>
       <c r="F44" t="s">
-        <v>71</v>
+        <v>266</v>
       </c>
       <c r="G44" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="H44" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="I44" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="J44" t="s">
-        <v>285</v>
+        <v>88</v>
       </c>
       <c r="M44" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="N44" t="s">
-        <v>287</v>
-      </c>
-      <c r="S44" t="s">
-        <v>288</v>
-      </c>
-      <c r="T44" t="s">
-        <v>289</v>
+        <v>273</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="W44" t="s">
         <v>63</v>
       </c>
       <c r="X44">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="B45" t="s">
-        <v>290</v>
+        <v>264</v>
+      </c>
+      <c r="D45" t="s">
+        <v>265</v>
+      </c>
+      <c r="E45" t="s">
+        <v>265</v>
       </c>
       <c r="F45" t="s">
-        <v>97</v>
+        <v>266</v>
       </c>
       <c r="G45" t="s">
-        <v>58</v>
+        <v>267</v>
       </c>
       <c r="H45" t="s">
-        <v>73</v>
+        <v>275</v>
+      </c>
+      <c r="I45" t="s">
+        <v>276</v>
       </c>
       <c r="J45" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="M45" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="N45" t="s">
-        <v>293</v>
-      </c>
-      <c r="S45" t="s">
-        <v>33</v>
-      </c>
-      <c r="T45" t="s">
-        <v>294</v>
+        <v>279</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="W45" t="s">
         <v>63</v>
@@ -4378,116 +4573,113 @@
     </row>
     <row r="46" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="B46" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="F46" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="G46" t="s">
-        <v>58</v>
+        <v>282</v>
       </c>
       <c r="H46" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="I46" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="J46" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="M46" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="N46" t="s">
-        <v>298</v>
-      </c>
-      <c r="S46" t="s">
-        <v>299</v>
+        <v>286</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>288</v>
       </c>
       <c r="W46" t="s">
         <v>63</v>
       </c>
       <c r="X46">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>300</v>
+        <v>239</v>
       </c>
       <c r="B47" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="F47" t="s">
-        <v>302</v>
+        <v>97</v>
       </c>
       <c r="G47" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H47" t="s">
-        <v>303</v>
-      </c>
-      <c r="I47" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="J47" t="s">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="M47" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="N47" t="s">
-        <v>305</v>
-      </c>
-      <c r="S47" t="s">
+        <v>292</v>
+      </c>
+      <c r="S47" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="T47" t="s">
-        <v>134</v>
+      <c r="T47" s="3" t="s">
+        <v>293</v>
       </c>
       <c r="W47" t="s">
         <v>63</v>
       </c>
       <c r="X47">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>300</v>
+        <v>239</v>
       </c>
       <c r="B48" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="F48" t="s">
-        <v>302</v>
+        <v>97</v>
       </c>
       <c r="G48" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H48" t="s">
-        <v>181</v>
+        <v>294</v>
       </c>
       <c r="I48" t="s">
         <v>59</v>
       </c>
       <c r="J48" t="s">
-        <v>159</v>
+        <v>295</v>
       </c>
       <c r="M48" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="N48" t="s">
-        <v>307</v>
-      </c>
-      <c r="S48" t="s">
-        <v>39</v>
-      </c>
-      <c r="T48" t="s">
-        <v>308</v>
+        <v>297</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>298</v>
       </c>
       <c r="W48" t="s">
         <v>63</v>
@@ -4498,233 +4690,233 @@
     </row>
     <row r="49" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>299</v>
+      </c>
+      <c r="B49" t="s">
         <v>300</v>
       </c>
-      <c r="B49" t="s">
+      <c r="F49" t="s">
         <v>301</v>
-      </c>
-      <c r="F49" t="s">
-        <v>302</v>
       </c>
       <c r="G49" t="s">
         <v>57</v>
       </c>
       <c r="H49" t="s">
-        <v>64</v>
+        <v>302</v>
       </c>
       <c r="I49" t="s">
-        <v>309</v>
+        <v>59</v>
       </c>
       <c r="J49" t="s">
-        <v>310</v>
+        <v>65</v>
       </c>
       <c r="M49" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="N49" t="s">
-        <v>312</v>
-      </c>
-      <c r="S49" t="s">
+        <v>304</v>
+      </c>
+      <c r="S49" s="3" t="s">
         <v>33</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="W49" t="s">
         <v>63</v>
       </c>
       <c r="X49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>299</v>
+      </c>
+      <c r="B50" t="s">
+        <v>300</v>
+      </c>
+      <c r="F50" t="s">
+        <v>301</v>
+      </c>
+      <c r="G50" t="s">
+        <v>57</v>
+      </c>
+      <c r="H50" t="s">
+        <v>180</v>
+      </c>
+      <c r="I50" t="s">
+        <v>59</v>
+      </c>
+      <c r="J50" t="s">
+        <v>158</v>
+      </c>
+      <c r="M50" t="s">
+        <v>305</v>
+      </c>
+      <c r="N50" t="s">
+        <v>306</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T50" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="W50" t="s">
+        <v>63</v>
+      </c>
+      <c r="X50">
         <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="M50" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="N50" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="S50" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="T50" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="W50" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="X50" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="B51" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="F51" t="s">
-        <v>189</v>
+        <v>301</v>
       </c>
       <c r="G51" t="s">
-        <v>315</v>
+        <v>57</v>
       </c>
       <c r="H51" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="I51" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="J51" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="M51" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="N51" t="s">
-        <v>324</v>
-      </c>
-      <c r="S51" t="s">
-        <v>39</v>
+        <v>311</v>
+      </c>
+      <c r="S51" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="W51" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="X51">
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>325</v>
-      </c>
-      <c r="B52" t="s">
-        <v>326</v>
-      </c>
-      <c r="F52" t="s">
-        <v>327</v>
-      </c>
-      <c r="G52" t="s">
-        <v>328</v>
-      </c>
-      <c r="H52" t="s">
-        <v>224</v>
-      </c>
-      <c r="I52" t="s">
-        <v>59</v>
-      </c>
-      <c r="J52" t="s">
-        <v>329</v>
-      </c>
-      <c r="M52" t="s">
-        <v>330</v>
-      </c>
-      <c r="N52" t="s">
-        <v>331</v>
-      </c>
-      <c r="S52" t="s">
-        <v>165</v>
-      </c>
-      <c r="W52" t="s">
-        <v>63</v>
-      </c>
-      <c r="X52">
-        <v>3</v>
+    <row r="52" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="S52" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="T52" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="W52" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="X52" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="B53" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="F53" t="s">
-        <v>108</v>
+        <v>188</v>
       </c>
       <c r="G53" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="H53" t="s">
-        <v>210</v>
+        <v>122</v>
       </c>
       <c r="I53" t="s">
-        <v>59</v>
+        <v>320</v>
       </c>
       <c r="J53" t="s">
-        <v>65</v>
+        <v>321</v>
       </c>
       <c r="M53" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="N53" t="s">
-        <v>336</v>
-      </c>
-      <c r="S53" t="s">
+        <v>323</v>
+      </c>
+      <c r="S53" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T53" t="s">
-        <v>177</v>
-      </c>
       <c r="W53" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="X53">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="B54" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F54" t="s">
-        <v>108</v>
+        <v>326</v>
       </c>
       <c r="G54" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H54" t="s">
-        <v>337</v>
+        <v>223</v>
       </c>
       <c r="I54" t="s">
         <v>59</v>
       </c>
       <c r="J54" t="s">
-        <v>65</v>
+        <v>328</v>
       </c>
       <c r="M54" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="N54" t="s">
-        <v>339</v>
-      </c>
-      <c r="S54" t="s">
-        <v>39</v>
-      </c>
-      <c r="T54" t="s">
-        <v>43</v>
+        <v>330</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="W54" t="s">
         <v>63</v>
@@ -4735,19 +4927,19 @@
     </row>
     <row r="55" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>331</v>
+      </c>
+      <c r="B55" t="s">
         <v>332</v>
-      </c>
-      <c r="B55" t="s">
-        <v>333</v>
       </c>
       <c r="F55" t="s">
         <v>108</v>
       </c>
       <c r="G55" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H55" t="s">
-        <v>340</v>
+        <v>209</v>
       </c>
       <c r="I55" t="s">
         <v>59</v>
@@ -4756,95 +4948,98 @@
         <v>65</v>
       </c>
       <c r="M55" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="N55" t="s">
-        <v>342</v>
-      </c>
-      <c r="S55" t="s">
-        <v>33</v>
+        <v>335</v>
+      </c>
+      <c r="S55" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T55" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="W55" t="s">
         <v>63</v>
       </c>
       <c r="X55">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="B56" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="F56" t="s">
-        <v>345</v>
+        <v>108</v>
       </c>
       <c r="G56" t="s">
-        <v>205</v>
+        <v>333</v>
       </c>
       <c r="H56" t="s">
-        <v>303</v>
+        <v>336</v>
       </c>
       <c r="I56" t="s">
-        <v>321</v>
+        <v>59</v>
       </c>
       <c r="J56" t="s">
-        <v>346</v>
+        <v>65</v>
       </c>
       <c r="M56" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="N56" t="s">
-        <v>348</v>
-      </c>
-      <c r="S56" t="s">
+        <v>338</v>
+      </c>
+      <c r="S56" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T56" t="s">
-        <v>275</v>
+      <c r="T56" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="W56" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="X56">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="B57" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="F57" t="s">
-        <v>345</v>
+        <v>108</v>
       </c>
       <c r="G57" t="s">
-        <v>205</v>
+        <v>333</v>
       </c>
       <c r="H57" t="s">
-        <v>58</v>
+        <v>339</v>
       </c>
       <c r="I57" t="s">
-        <v>321</v>
+        <v>59</v>
       </c>
       <c r="J57" t="s">
-        <v>349</v>
+        <v>65</v>
       </c>
       <c r="M57" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="N57" t="s">
-        <v>351</v>
-      </c>
-      <c r="S57" t="s">
-        <v>39</v>
+        <v>341</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="W57" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="X57">
         <v>3</v>
@@ -4852,110 +5047,113 @@
     </row>
     <row r="58" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="B58" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="F58" t="s">
-        <v>172</v>
+        <v>344</v>
       </c>
       <c r="G58" t="s">
-        <v>354</v>
+        <v>204</v>
       </c>
       <c r="H58" t="s">
-        <v>166</v>
+        <v>302</v>
       </c>
       <c r="I58" t="s">
-        <v>59</v>
+        <v>320</v>
       </c>
       <c r="J58" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="M58" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="N58" t="s">
-        <v>357</v>
-      </c>
-      <c r="S58" t="s">
-        <v>33</v>
+        <v>347</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="W58" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="X58">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="B59" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="F59" t="s">
-        <v>172</v>
+        <v>344</v>
       </c>
       <c r="G59" t="s">
-        <v>354</v>
+        <v>204</v>
       </c>
       <c r="H59" t="s">
-        <v>173</v>
+        <v>58</v>
       </c>
       <c r="I59" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="J59" t="s">
-        <v>137</v>
+        <v>348</v>
       </c>
       <c r="M59" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="N59" t="s">
-        <v>360</v>
-      </c>
-      <c r="S59" t="s">
-        <v>33</v>
-      </c>
-      <c r="T59" t="s">
-        <v>134</v>
+        <v>350</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="W59" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="X59">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>351</v>
+      </c>
+      <c r="B60" t="s">
         <v>352</v>
       </c>
-      <c r="B60" t="s">
+      <c r="F60" t="s">
+        <v>171</v>
+      </c>
+      <c r="G60" t="s">
         <v>353</v>
       </c>
-      <c r="F60" t="s">
-        <v>172</v>
-      </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
+        <v>165</v>
+      </c>
+      <c r="I60" t="s">
+        <v>59</v>
+      </c>
+      <c r="J60" t="s">
         <v>354</v>
       </c>
-      <c r="H60" t="s">
-        <v>216</v>
-      </c>
-      <c r="J60" t="s">
-        <v>361</v>
-      </c>
       <c r="M60" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="N60" t="s">
-        <v>363</v>
-      </c>
-      <c r="S60" t="s">
-        <v>364</v>
+        <v>356</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="W60" t="s">
         <v>63</v>
@@ -4966,75 +5164,75 @@
     </row>
     <row r="61" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>351</v>
+      </c>
+      <c r="B61" t="s">
         <v>352</v>
       </c>
-      <c r="B61" t="s">
+      <c r="F61" t="s">
+        <v>171</v>
+      </c>
+      <c r="G61" t="s">
         <v>353</v>
       </c>
-      <c r="F61" t="s">
+      <c r="H61" t="s">
         <v>172</v>
       </c>
-      <c r="G61" t="s">
-        <v>354</v>
-      </c>
-      <c r="H61" t="s">
-        <v>365</v>
-      </c>
       <c r="I61" t="s">
-        <v>59</v>
+        <v>357</v>
       </c>
       <c r="J61" t="s">
-        <v>366</v>
+        <v>137</v>
       </c>
       <c r="M61" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="N61" t="s">
-        <v>368</v>
-      </c>
-      <c r="S61" t="s">
-        <v>185</v>
+        <v>359</v>
+      </c>
+      <c r="S61" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T61" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="W61" t="s">
         <v>63</v>
       </c>
       <c r="X61">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="B62" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="F62" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="G62" t="s">
-        <v>58</v>
+        <v>353</v>
       </c>
       <c r="H62" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="J62" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M62" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="N62" t="s">
-        <v>373</v>
-      </c>
-      <c r="S62" t="s">
-        <v>39</v>
-      </c>
-      <c r="T62" t="s">
-        <v>374</v>
+        <v>362</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>363</v>
       </c>
       <c r="W62" t="s">
-        <v>375</v>
+        <v>63</v>
       </c>
       <c r="X62">
         <v>3</v>
@@ -5042,81 +5240,75 @@
     </row>
     <row r="63" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="B63" t="s">
-        <v>377</v>
+        <v>352</v>
       </c>
       <c r="F63" t="s">
-        <v>378</v>
+        <v>171</v>
       </c>
       <c r="G63" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
       <c r="H63" t="s">
-        <v>337</v>
+        <v>364</v>
       </c>
       <c r="I63" t="s">
-        <v>321</v>
+        <v>59</v>
       </c>
       <c r="J63" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="M63" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="N63" t="s">
-        <v>382</v>
-      </c>
-      <c r="S63" t="s">
-        <v>33</v>
-      </c>
-      <c r="T63" t="s">
-        <v>177</v>
+        <v>367</v>
+      </c>
+      <c r="S63" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="W63" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="X63">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B64" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="F64" t="s">
-        <v>378</v>
+        <v>144</v>
       </c>
       <c r="G64" t="s">
-        <v>379</v>
+        <v>58</v>
       </c>
       <c r="H64" t="s">
-        <v>249</v>
-      </c>
-      <c r="I64" t="s">
-        <v>383</v>
+        <v>227</v>
       </c>
       <c r="J64" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="M64" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="N64" t="s">
-        <v>386</v>
-      </c>
-      <c r="S64" t="s">
-        <v>33</v>
-      </c>
-      <c r="T64" t="s">
-        <v>177</v>
+        <v>372</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T64" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="W64" t="s">
-        <v>93</v>
+        <v>374</v>
       </c>
       <c r="X64">
         <v>3</v>
@@ -5124,309 +5316,318 @@
     </row>
     <row r="65" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="B65" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="F65" t="s">
-        <v>172</v>
+        <v>377</v>
       </c>
       <c r="G65" t="s">
-        <v>72</v>
+        <v>378</v>
       </c>
       <c r="H65" t="s">
-        <v>135</v>
+        <v>336</v>
       </c>
       <c r="I65" t="s">
-        <v>59</v>
+        <v>320</v>
       </c>
       <c r="J65" t="s">
-        <v>65</v>
+        <v>379</v>
       </c>
       <c r="M65" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="N65" t="s">
-        <v>390</v>
-      </c>
-      <c r="S65" t="s">
-        <v>391</v>
-      </c>
-      <c r="T65" t="s">
-        <v>134</v>
+        <v>381</v>
+      </c>
+      <c r="S65" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T65" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="W65" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="X65">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="B66" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="F66" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="G66" t="s">
-        <v>178</v>
+        <v>378</v>
       </c>
       <c r="H66" t="s">
-        <v>395</v>
+        <v>248</v>
       </c>
       <c r="I66" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="J66" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="M66" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="N66" t="s">
-        <v>399</v>
-      </c>
-      <c r="S66" t="s">
-        <v>400</v>
-      </c>
-      <c r="T66" t="s">
-        <v>308</v>
+        <v>385</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="W66" t="s">
-        <v>193</v>
+        <v>93</v>
       </c>
       <c r="X66">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>127</v>
+        <v>386</v>
       </c>
       <c r="B67" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="F67" t="s">
-        <v>402</v>
+        <v>171</v>
       </c>
       <c r="G67" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="H67" t="s">
-        <v>212</v>
+        <v>135</v>
       </c>
       <c r="I67" t="s">
-        <v>403</v>
+        <v>59</v>
       </c>
       <c r="J67" t="s">
-        <v>404</v>
+        <v>65</v>
       </c>
       <c r="M67" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="N67" t="s">
-        <v>406</v>
-      </c>
-      <c r="S67" t="s">
-        <v>407</v>
+        <v>389</v>
+      </c>
+      <c r="S67" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="T67" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="W67" t="s">
-        <v>193</v>
+        <v>63</v>
       </c>
       <c r="X67">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="B68" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="F68" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="G68" t="s">
-        <v>411</v>
+        <v>177</v>
       </c>
       <c r="H68" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="I68" t="s">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="J68" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="M68" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="N68" t="s">
-        <v>416</v>
-      </c>
-      <c r="S68" t="s">
-        <v>299</v>
+        <v>398</v>
+      </c>
+      <c r="S68" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="T68" s="3" t="s">
+        <v>307</v>
       </c>
       <c r="W68" t="s">
-        <v>417</v>
+        <v>192</v>
       </c>
       <c r="X68">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>418</v>
+        <v>127</v>
       </c>
       <c r="B69" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="F69" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="G69" t="s">
-        <v>421</v>
+        <v>129</v>
       </c>
       <c r="H69" t="s">
-        <v>422</v>
+        <v>211</v>
       </c>
       <c r="I69" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="J69" t="s">
-        <v>424</v>
+        <v>403</v>
       </c>
       <c r="M69" t="s">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="N69" t="s">
-        <v>426</v>
-      </c>
-      <c r="S69" t="s">
-        <v>39</v>
-      </c>
-      <c r="T69" t="s">
-        <v>427</v>
+        <v>405</v>
+      </c>
+      <c r="S69" s="3" t="s">
+        <v>406</v>
       </c>
       <c r="W69" t="s">
-        <v>53</v>
+        <v>192</v>
       </c>
       <c r="X69">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>428</v>
+        <v>407</v>
       </c>
       <c r="B70" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="F70" t="s">
-        <v>144</v>
+        <v>409</v>
       </c>
       <c r="G70" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="H70" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="I70" t="s">
-        <v>29</v>
+        <v>412</v>
       </c>
       <c r="J70" t="s">
-        <v>432</v>
+        <v>413</v>
       </c>
       <c r="M70" t="s">
-        <v>433</v>
+        <v>414</v>
       </c>
       <c r="N70" t="s">
-        <v>434</v>
-      </c>
-      <c r="S70" t="s">
-        <v>33</v>
+        <v>415</v>
+      </c>
+      <c r="S70" s="3" t="s">
+        <v>298</v>
       </c>
       <c r="W70" t="s">
-        <v>35</v>
+        <v>416</v>
       </c>
       <c r="X70">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="B71" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="F71" t="s">
-        <v>144</v>
+        <v>419</v>
       </c>
       <c r="G71" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="H71" t="s">
-        <v>435</v>
+        <v>421</v>
+      </c>
+      <c r="I71" t="s">
+        <v>422</v>
       </c>
       <c r="J71" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="M71" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="N71" t="s">
-        <v>438</v>
-      </c>
-      <c r="S71" t="s">
-        <v>33</v>
+        <v>425</v>
+      </c>
+      <c r="S71" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T71" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="W71" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="X71">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="B72" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="F72" t="s">
-        <v>378</v>
+        <v>144</v>
       </c>
       <c r="G72" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="H72" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="I72" t="s">
-        <v>442</v>
+        <v>29</v>
       </c>
       <c r="J72" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="M72" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="N72" t="s">
-        <v>445</v>
-      </c>
-      <c r="S72" t="s">
-        <v>39</v>
+        <v>433</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="W72" t="s">
-        <v>375</v>
+        <v>35</v>
       </c>
       <c r="X72">
         <v>1</v>
@@ -5434,163 +5635,154 @@
     </row>
     <row r="73" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="B73" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="F73" t="s">
-        <v>420</v>
+        <v>144</v>
       </c>
       <c r="G73" t="s">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="H73" t="s">
-        <v>449</v>
-      </c>
-      <c r="I73" t="s">
-        <v>403</v>
+        <v>434</v>
       </c>
       <c r="J73" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="M73" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="N73" t="s">
-        <v>452</v>
-      </c>
-      <c r="S73" t="s">
+        <v>437</v>
+      </c>
+      <c r="S73" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="T73" t="s">
-        <v>308</v>
-      </c>
       <c r="W73" t="s">
-        <v>193</v>
+        <v>35</v>
       </c>
       <c r="X73">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="B74" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="F74" t="s">
+        <v>377</v>
+      </c>
+      <c r="G74" t="s">
         <v>420</v>
       </c>
-      <c r="G74" t="s">
-        <v>448</v>
-      </c>
       <c r="H74" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="I74" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="J74" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="M74" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="N74" t="s">
-        <v>457</v>
-      </c>
-      <c r="S74" t="s">
-        <v>33</v>
-      </c>
-      <c r="T74" t="s">
-        <v>134</v>
+        <v>444</v>
+      </c>
+      <c r="S74" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="W74" t="s">
-        <v>193</v>
+        <v>374</v>
       </c>
       <c r="X74">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="B75" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="F75" t="s">
-        <v>460</v>
+        <v>419</v>
       </c>
       <c r="G75" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="H75" t="s">
-        <v>48</v>
+        <v>448</v>
       </c>
       <c r="I75" t="s">
-        <v>49</v>
+        <v>402</v>
       </c>
       <c r="J75" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="M75" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="N75" t="s">
-        <v>464</v>
-      </c>
-      <c r="S75" t="s">
-        <v>39</v>
-      </c>
-      <c r="T75" t="s">
-        <v>465</v>
+        <v>451</v>
+      </c>
+      <c r="S75" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T75" s="3" t="s">
+        <v>307</v>
       </c>
       <c r="W75" t="s">
-        <v>53</v>
+        <v>192</v>
       </c>
       <c r="X75">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>466</v>
+        <v>445</v>
       </c>
       <c r="B76" t="s">
-        <v>467</v>
+        <v>446</v>
       </c>
       <c r="F76" t="s">
-        <v>122</v>
+        <v>419</v>
       </c>
       <c r="G76" t="s">
-        <v>468</v>
+        <v>447</v>
       </c>
       <c r="H76" t="s">
-        <v>181</v>
+        <v>452</v>
       </c>
       <c r="I76" t="s">
-        <v>59</v>
+        <v>453</v>
       </c>
       <c r="J76" t="s">
-        <v>65</v>
+        <v>454</v>
       </c>
       <c r="M76" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="N76" t="s">
-        <v>470</v>
-      </c>
-      <c r="S76" t="s">
+        <v>456</v>
+      </c>
+      <c r="S76" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="T76" t="s">
-        <v>294</v>
+      <c r="T76" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="W76" t="s">
-        <v>63</v>
+        <v>192</v>
       </c>
       <c r="X76">
         <v>3</v>
@@ -5598,40 +5790,40 @@
     </row>
     <row r="77" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="B77" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="F77" t="s">
-        <v>122</v>
+        <v>459</v>
       </c>
       <c r="G77" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="H77" t="s">
-        <v>166</v>
+        <v>48</v>
       </c>
       <c r="I77" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="J77" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="M77" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="N77" t="s">
-        <v>473</v>
-      </c>
-      <c r="S77" t="s">
-        <v>33</v>
-      </c>
-      <c r="T77" t="s">
-        <v>474</v>
+        <v>463</v>
+      </c>
+      <c r="S77" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T77" s="3" t="s">
+        <v>464</v>
       </c>
       <c r="W77" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="X77">
         <v>1</v>
@@ -5639,116 +5831,122 @@
     </row>
     <row r="78" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="B78" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="F78" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="G78" t="s">
-        <v>57</v>
+        <v>467</v>
       </c>
       <c r="H78" t="s">
-        <v>477</v>
+        <v>180</v>
       </c>
       <c r="I78" t="s">
-        <v>442</v>
+        <v>59</v>
       </c>
       <c r="J78" t="s">
-        <v>478</v>
+        <v>65</v>
       </c>
       <c r="M78" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="N78" t="s">
-        <v>480</v>
-      </c>
-      <c r="S78" t="s">
+        <v>469</v>
+      </c>
+      <c r="S78" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="T78" t="s">
-        <v>374</v>
+      <c r="T78" s="3" t="s">
+        <v>293</v>
       </c>
       <c r="W78" t="s">
-        <v>375</v>
+        <v>63</v>
       </c>
       <c r="X78">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="B79" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="F79" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="G79" t="s">
-        <v>115</v>
+        <v>467</v>
       </c>
       <c r="H79" t="s">
-        <v>483</v>
+        <v>165</v>
       </c>
       <c r="I79" t="s">
         <v>59</v>
       </c>
       <c r="J79" t="s">
-        <v>182</v>
+        <v>470</v>
       </c>
       <c r="M79" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="N79" t="s">
-        <v>485</v>
-      </c>
-      <c r="S79" t="s">
-        <v>486</v>
+        <v>472</v>
+      </c>
+      <c r="S79" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T79" s="3" t="s">
+        <v>473</v>
       </c>
       <c r="W79" t="s">
         <v>63</v>
       </c>
       <c r="X79">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="B80" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="F80" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="G80" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="H80" t="s">
-        <v>303</v>
+        <v>476</v>
       </c>
       <c r="I80" t="s">
-        <v>487</v>
+        <v>441</v>
       </c>
       <c r="J80" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="M80" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="N80" t="s">
-        <v>490</v>
-      </c>
-      <c r="S80" t="s">
-        <v>491</v>
+        <v>479</v>
+      </c>
+      <c r="S80" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T80" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="W80" t="s">
-        <v>63</v>
+        <v>374</v>
       </c>
       <c r="X80">
         <v>2</v>
@@ -5756,34 +5954,34 @@
     </row>
     <row r="81" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="B81" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="F81" t="s">
-        <v>143</v>
+        <v>46</v>
       </c>
       <c r="G81" t="s">
-        <v>494</v>
+        <v>115</v>
       </c>
       <c r="H81" t="s">
-        <v>402</v>
+        <v>482</v>
       </c>
       <c r="I81" t="s">
-        <v>495</v>
+        <v>59</v>
       </c>
       <c r="J81" t="s">
-        <v>496</v>
+        <v>181</v>
       </c>
       <c r="M81" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="N81" t="s">
-        <v>498</v>
-      </c>
-      <c r="S81" t="s">
-        <v>499</v>
+        <v>484</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>485</v>
       </c>
       <c r="W81" t="s">
         <v>63</v>
@@ -5794,95 +5992,95 @@
     </row>
     <row r="82" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="B82" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="F82" t="s">
-        <v>143</v>
+        <v>46</v>
       </c>
       <c r="G82" t="s">
-        <v>494</v>
+        <v>115</v>
       </c>
       <c r="H82" t="s">
-        <v>340</v>
+        <v>302</v>
       </c>
       <c r="I82" t="s">
-        <v>59</v>
+        <v>486</v>
       </c>
       <c r="J82" t="s">
-        <v>65</v>
+        <v>487</v>
       </c>
       <c r="M82" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="N82" t="s">
-        <v>501</v>
-      </c>
-      <c r="S82" t="s">
-        <v>33</v>
+        <v>489</v>
+      </c>
+      <c r="S82" s="3" t="s">
+        <v>490</v>
       </c>
       <c r="W82" t="s">
         <v>63</v>
       </c>
       <c r="X82">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="B83" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="F83" t="s">
-        <v>228</v>
+        <v>143</v>
       </c>
       <c r="G83" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="H83" t="s">
-        <v>505</v>
+        <v>401</v>
       </c>
       <c r="I83" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="J83" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="M83" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="N83" t="s">
-        <v>509</v>
-      </c>
-      <c r="S83" t="s">
-        <v>33</v>
+        <v>497</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>498</v>
       </c>
       <c r="W83" t="s">
-        <v>510</v>
+        <v>63</v>
       </c>
       <c r="X83">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="B84" t="s">
-        <v>512</v>
+        <v>492</v>
       </c>
       <c r="F84" t="s">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="G84" t="s">
-        <v>48</v>
+        <v>493</v>
       </c>
       <c r="H84" t="s">
-        <v>162</v>
+        <v>339</v>
       </c>
       <c r="I84" t="s">
         <v>59</v>
@@ -5891,16 +6089,13 @@
         <v>65</v>
       </c>
       <c r="M84" t="s">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="N84" t="s">
-        <v>514</v>
-      </c>
-      <c r="S84" t="s">
-        <v>39</v>
-      </c>
-      <c r="T84" t="s">
-        <v>177</v>
+        <v>500</v>
+      </c>
+      <c r="S84" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="W84" t="s">
         <v>63</v>
@@ -5911,160 +6106,157 @@
     </row>
     <row r="85" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="B85" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="F85" t="s">
-        <v>517</v>
+        <v>227</v>
       </c>
       <c r="G85" t="s">
-        <v>28</v>
+        <v>503</v>
       </c>
       <c r="H85" t="s">
-        <v>410</v>
+        <v>504</v>
       </c>
       <c r="I85" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="J85" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="M85" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="N85" t="s">
-        <v>521</v>
-      </c>
-      <c r="S85" t="s">
+        <v>508</v>
+      </c>
+      <c r="S85" s="3" t="s">
         <v>33</v>
       </c>
       <c r="W85" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="X85">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="B86" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="F86" t="s">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="G86" t="s">
-        <v>181</v>
+        <v>48</v>
       </c>
       <c r="H86" t="s">
-        <v>460</v>
+        <v>161</v>
       </c>
       <c r="I86" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="J86" t="s">
-        <v>285</v>
+        <v>65</v>
       </c>
       <c r="M86" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="N86" t="s">
-        <v>526</v>
-      </c>
-      <c r="S86" t="s">
+        <v>513</v>
+      </c>
+      <c r="S86" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T86" t="s">
-        <v>527</v>
+      <c r="T86" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="W86" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="X86">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="B87" t="s">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="F87" t="s">
-        <v>394</v>
+        <v>516</v>
       </c>
       <c r="G87" t="s">
-        <v>378</v>
+        <v>28</v>
       </c>
       <c r="H87" t="s">
-        <v>108</v>
+        <v>409</v>
       </c>
       <c r="I87" t="s">
-        <v>59</v>
+        <v>517</v>
       </c>
       <c r="J87" t="s">
-        <v>88</v>
+        <v>518</v>
       </c>
       <c r="M87" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="N87" t="s">
-        <v>531</v>
-      </c>
-      <c r="S87" t="s">
-        <v>39</v>
-      </c>
-      <c r="T87" t="s">
-        <v>532</v>
+        <v>520</v>
+      </c>
+      <c r="S87" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="W87" t="s">
-        <v>253</v>
+        <v>521</v>
       </c>
       <c r="X87">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="B88" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="F88" t="s">
-        <v>394</v>
+        <v>144</v>
       </c>
       <c r="G88" t="s">
-        <v>378</v>
+        <v>180</v>
       </c>
       <c r="H88" t="s">
-        <v>378</v>
+        <v>459</v>
       </c>
       <c r="I88" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="J88" t="s">
-        <v>65</v>
+        <v>284</v>
       </c>
       <c r="M88" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="N88" t="s">
-        <v>534</v>
-      </c>
-      <c r="S88" t="s">
+        <v>525</v>
+      </c>
+      <c r="S88" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T88" t="s">
-        <v>535</v>
+      <c r="T88" s="3" t="s">
+        <v>526</v>
       </c>
       <c r="W88" t="s">
-        <v>253</v>
+        <v>53</v>
       </c>
       <c r="X88">
         <v>1</v>
@@ -6072,153 +6264,156 @@
     </row>
     <row r="89" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>69</v>
+        <v>527</v>
       </c>
       <c r="B89" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="F89" t="s">
-        <v>537</v>
+        <v>393</v>
       </c>
       <c r="G89" t="s">
-        <v>73</v>
+        <v>377</v>
       </c>
       <c r="H89" t="s">
-        <v>538</v>
+        <v>108</v>
       </c>
       <c r="I89" t="s">
         <v>59</v>
       </c>
       <c r="J89" t="s">
-        <v>539</v>
+        <v>88</v>
       </c>
       <c r="M89" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="N89" t="s">
-        <v>541</v>
-      </c>
-      <c r="S89" t="s">
-        <v>33</v>
-      </c>
-      <c r="T89" t="s">
-        <v>542</v>
+        <v>530</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>531</v>
       </c>
       <c r="W89" t="s">
-        <v>63</v>
+        <v>252</v>
       </c>
       <c r="X89">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="B90" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="F90" t="s">
-        <v>85</v>
+        <v>393</v>
       </c>
       <c r="G90" t="s">
-        <v>545</v>
+        <v>377</v>
       </c>
       <c r="H90" t="s">
-        <v>546</v>
+        <v>377</v>
       </c>
       <c r="I90" t="s">
-        <v>116</v>
+        <v>59</v>
       </c>
       <c r="J90" t="s">
-        <v>547</v>
+        <v>65</v>
       </c>
       <c r="M90" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="N90" t="s">
-        <v>549</v>
-      </c>
-      <c r="S90" t="s">
-        <v>33</v>
+        <v>533</v>
+      </c>
+      <c r="S90" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T90" s="3" t="s">
+        <v>534</v>
       </c>
       <c r="W90" t="s">
-        <v>114</v>
+        <v>252</v>
       </c>
       <c r="X90">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>446</v>
+        <v>69</v>
       </c>
       <c r="B91" t="s">
-        <v>550</v>
+        <v>535</v>
       </c>
       <c r="F91" t="s">
-        <v>551</v>
+        <v>536</v>
       </c>
       <c r="G91" t="s">
-        <v>411</v>
+        <v>73</v>
       </c>
       <c r="H91" t="s">
-        <v>453</v>
+        <v>537</v>
       </c>
       <c r="I91" t="s">
-        <v>552</v>
+        <v>59</v>
       </c>
       <c r="J91" t="s">
-        <v>553</v>
+        <v>538</v>
       </c>
       <c r="M91" t="s">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="N91" t="s">
-        <v>555</v>
-      </c>
-      <c r="S91" t="s">
+        <v>540</v>
+      </c>
+      <c r="S91" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="T91" t="s">
-        <v>43</v>
+      <c r="T91" s="3" t="s">
+        <v>541</v>
       </c>
       <c r="W91" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="X91">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="B92" t="s">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="F92" t="s">
-        <v>558</v>
+        <v>85</v>
       </c>
       <c r="G92" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="H92" t="s">
         <v>545</v>
       </c>
       <c r="I92" t="s">
-        <v>559</v>
+        <v>116</v>
       </c>
       <c r="J92" t="s">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="M92" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="N92" t="s">
-        <v>562</v>
-      </c>
-      <c r="S92" t="s">
+        <v>548</v>
+      </c>
+      <c r="S92" s="3" t="s">
         <v>33</v>
       </c>
       <c r="W92" t="s">
@@ -6230,84 +6425,81 @@
     </row>
     <row r="93" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>69</v>
+        <v>445</v>
       </c>
       <c r="B93" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="F93" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="G93" t="s">
-        <v>283</v>
+        <v>410</v>
       </c>
       <c r="H93" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="I93" t="s">
-        <v>116</v>
+        <v>551</v>
       </c>
       <c r="J93" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="M93" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="N93" t="s">
-        <v>567</v>
-      </c>
-      <c r="S93" t="s">
+        <v>554</v>
+      </c>
+      <c r="S93" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="T93" t="s">
-        <v>101</v>
+      <c r="T93" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="W93" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="X93">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>69</v>
+        <v>555</v>
       </c>
       <c r="B94" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="F94" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="G94" t="s">
-        <v>283</v>
+        <v>550</v>
       </c>
       <c r="H94" t="s">
-        <v>568</v>
+        <v>544</v>
       </c>
       <c r="I94" t="s">
-        <v>59</v>
+        <v>558</v>
       </c>
       <c r="J94" t="s">
-        <v>213</v>
+        <v>559</v>
       </c>
       <c r="M94" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="N94" t="s">
-        <v>570</v>
-      </c>
-      <c r="S94" t="s">
+        <v>561</v>
+      </c>
+      <c r="S94" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="T94" t="s">
-        <v>571</v>
-      </c>
       <c r="W94" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="X94">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6315,31 +6507,34 @@
         <v>69</v>
       </c>
       <c r="B95" t="s">
+        <v>562</v>
+      </c>
+      <c r="F95" t="s">
         <v>563</v>
       </c>
-      <c r="F95" t="s">
+      <c r="G95" t="s">
+        <v>282</v>
+      </c>
+      <c r="H95" t="s">
+        <v>448</v>
+      </c>
+      <c r="I95" t="s">
+        <v>116</v>
+      </c>
+      <c r="J95" t="s">
         <v>564</v>
       </c>
-      <c r="G95" t="s">
-        <v>283</v>
-      </c>
-      <c r="H95" t="s">
-        <v>572</v>
-      </c>
-      <c r="I95" t="s">
-        <v>59</v>
-      </c>
-      <c r="J95" t="s">
-        <v>213</v>
-      </c>
       <c r="M95" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="N95" t="s">
-        <v>574</v>
-      </c>
-      <c r="S95" t="s">
-        <v>39</v>
+        <v>566</v>
+      </c>
+      <c r="S95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T95" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="W95" t="s">
         <v>63</v>
@@ -6353,40 +6548,40 @@
         <v>69</v>
       </c>
       <c r="B96" t="s">
+        <v>562</v>
+      </c>
+      <c r="F96" t="s">
         <v>563</v>
       </c>
-      <c r="F96" t="s">
-        <v>564</v>
-      </c>
       <c r="G96" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H96" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="I96" t="s">
-        <v>576</v>
+        <v>59</v>
       </c>
       <c r="J96" t="s">
-        <v>577</v>
+        <v>212</v>
       </c>
       <c r="M96" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="N96" t="s">
-        <v>579</v>
-      </c>
-      <c r="S96" t="s">
+        <v>569</v>
+      </c>
+      <c r="S96" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="T96" t="s">
-        <v>580</v>
+      <c r="T96" s="3" t="s">
+        <v>570</v>
       </c>
       <c r="W96" t="s">
         <v>63</v>
       </c>
       <c r="X96">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6394,34 +6589,31 @@
         <v>69</v>
       </c>
       <c r="B97" t="s">
+        <v>562</v>
+      </c>
+      <c r="F97" t="s">
         <v>563</v>
       </c>
-      <c r="F97" t="s">
-        <v>564</v>
-      </c>
       <c r="G97" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H97" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="I97" t="s">
         <v>59</v>
       </c>
       <c r="J97" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M97" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="N97" t="s">
-        <v>583</v>
-      </c>
-      <c r="S97" t="s">
-        <v>33</v>
-      </c>
-      <c r="T97" t="s">
-        <v>584</v>
+        <v>573</v>
+      </c>
+      <c r="S97" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="W97" t="s">
         <v>63</v>
@@ -6432,78 +6624,81 @@
     </row>
     <row r="98" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>585</v>
+        <v>69</v>
       </c>
       <c r="B98" t="s">
-        <v>586</v>
+        <v>562</v>
       </c>
       <c r="F98" t="s">
-        <v>587</v>
+        <v>563</v>
       </c>
       <c r="G98" t="s">
-        <v>205</v>
+        <v>282</v>
       </c>
       <c r="H98" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="I98" t="s">
-        <v>79</v>
+        <v>575</v>
       </c>
       <c r="J98" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="M98" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="N98" t="s">
-        <v>591</v>
-      </c>
-      <c r="S98" t="s">
-        <v>39</v>
-      </c>
-      <c r="T98" t="s">
-        <v>427</v>
+        <v>578</v>
+      </c>
+      <c r="S98" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T98" s="3" t="s">
+        <v>579</v>
       </c>
       <c r="W98" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="X98">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>585</v>
+        <v>69</v>
       </c>
       <c r="B99" t="s">
-        <v>586</v>
+        <v>562</v>
       </c>
       <c r="F99" t="s">
-        <v>587</v>
+        <v>563</v>
       </c>
       <c r="G99" t="s">
-        <v>205</v>
+        <v>282</v>
       </c>
       <c r="H99" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="I99" t="s">
-        <v>593</v>
+        <v>59</v>
       </c>
       <c r="J99" t="s">
-        <v>594</v>
+        <v>212</v>
       </c>
       <c r="M99" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="N99" t="s">
-        <v>596</v>
-      </c>
-      <c r="S99" t="s">
-        <v>39</v>
+        <v>582</v>
+      </c>
+      <c r="S99" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T99" s="3" t="s">
+        <v>583</v>
       </c>
       <c r="W99" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="X99">
         <v>3</v>
@@ -6511,81 +6706,78 @@
     </row>
     <row r="100" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="B100" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="F100" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="G100" t="s">
+        <v>204</v>
+      </c>
+      <c r="H100" t="s">
+        <v>587</v>
+      </c>
+      <c r="I100" t="s">
+        <v>79</v>
+      </c>
+      <c r="J100" t="s">
         <v>588</v>
       </c>
-      <c r="H100" t="s">
-        <v>108</v>
-      </c>
-      <c r="I100" t="s">
-        <v>59</v>
-      </c>
-      <c r="J100" t="s">
-        <v>88</v>
-      </c>
       <c r="M100" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="N100" t="s">
-        <v>601</v>
-      </c>
-      <c r="S100" t="s">
-        <v>33</v>
-      </c>
-      <c r="T100" t="s">
-        <v>43</v>
+        <v>590</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="W100" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="X100">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="B101" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="F101" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="G101" t="s">
-        <v>588</v>
+        <v>204</v>
       </c>
       <c r="H101" t="s">
-        <v>108</v>
+        <v>591</v>
       </c>
       <c r="I101" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="J101" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="M101" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="N101" t="s">
-        <v>605</v>
-      </c>
-      <c r="S101" t="s">
+        <v>595</v>
+      </c>
+      <c r="S101" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T101" t="s">
-        <v>606</v>
-      </c>
       <c r="W101" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="X101">
         <v>3</v>
@@ -6593,37 +6785,37 @@
     </row>
     <row r="102" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>596</v>
+      </c>
+      <c r="B102" t="s">
         <v>597</v>
       </c>
-      <c r="B102" t="s">
+      <c r="F102" t="s">
         <v>598</v>
       </c>
-      <c r="F102" t="s">
+      <c r="G102" t="s">
+        <v>587</v>
+      </c>
+      <c r="H102" t="s">
+        <v>108</v>
+      </c>
+      <c r="I102" t="s">
+        <v>59</v>
+      </c>
+      <c r="J102" t="s">
+        <v>88</v>
+      </c>
+      <c r="M102" t="s">
         <v>599</v>
       </c>
-      <c r="G102" t="s">
-        <v>588</v>
-      </c>
-      <c r="H102" t="s">
-        <v>410</v>
-      </c>
-      <c r="I102" t="s">
-        <v>79</v>
-      </c>
-      <c r="J102" t="s">
-        <v>589</v>
-      </c>
-      <c r="M102" t="s">
-        <v>607</v>
-      </c>
       <c r="N102" t="s">
-        <v>608</v>
-      </c>
-      <c r="S102" t="s">
+        <v>600</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="T102" t="s">
-        <v>542</v>
+      <c r="T102" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="W102" t="s">
         <v>63</v>
@@ -6634,72 +6826,78 @@
     </row>
     <row r="103" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>596</v>
+      </c>
+      <c r="B103" t="s">
         <v>597</v>
       </c>
-      <c r="B103" t="s">
+      <c r="F103" t="s">
         <v>598</v>
       </c>
-      <c r="F103" t="s">
-        <v>599</v>
-      </c>
       <c r="G103" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H103" t="s">
-        <v>248</v>
+        <v>108</v>
       </c>
       <c r="I103" t="s">
-        <v>59</v>
+        <v>601</v>
       </c>
       <c r="J103" t="s">
-        <v>329</v>
+        <v>602</v>
       </c>
       <c r="M103" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="N103" t="s">
-        <v>610</v>
-      </c>
-      <c r="S103" t="s">
-        <v>165</v>
+        <v>604</v>
+      </c>
+      <c r="S103" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T103" s="3" t="s">
+        <v>605</v>
       </c>
       <c r="W103" t="s">
         <v>63</v>
       </c>
       <c r="X103">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>596</v>
+      </c>
+      <c r="B104" t="s">
         <v>597</v>
       </c>
-      <c r="B104" t="s">
+      <c r="F104" t="s">
         <v>598</v>
       </c>
-      <c r="F104" t="s">
-        <v>599</v>
-      </c>
       <c r="G104" t="s">
+        <v>587</v>
+      </c>
+      <c r="H104" t="s">
+        <v>409</v>
+      </c>
+      <c r="I104" t="s">
+        <v>79</v>
+      </c>
+      <c r="J104" t="s">
         <v>588</v>
       </c>
-      <c r="H104" t="s">
-        <v>256</v>
-      </c>
-      <c r="I104" t="s">
-        <v>59</v>
-      </c>
-      <c r="J104" t="s">
-        <v>611</v>
-      </c>
       <c r="M104" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="N104" t="s">
-        <v>613</v>
-      </c>
-      <c r="S104" t="s">
-        <v>165</v>
+        <v>607</v>
+      </c>
+      <c r="S104" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T104" s="3" t="s">
+        <v>541</v>
       </c>
       <c r="W104" t="s">
         <v>63</v>
@@ -6710,195 +6908,192 @@
     </row>
     <row r="105" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>596</v>
+      </c>
+      <c r="B105" t="s">
         <v>597</v>
       </c>
-      <c r="B105" t="s">
+      <c r="F105" t="s">
         <v>598</v>
       </c>
-      <c r="F105" t="s">
-        <v>599</v>
-      </c>
       <c r="G105" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H105" t="s">
-        <v>122</v>
+        <v>247</v>
       </c>
       <c r="I105" t="s">
-        <v>614</v>
+        <v>59</v>
       </c>
       <c r="J105" t="s">
-        <v>615</v>
+        <v>328</v>
       </c>
       <c r="M105" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="N105" t="s">
-        <v>617</v>
-      </c>
-      <c r="S105" t="s">
-        <v>33</v>
-      </c>
-      <c r="T105" t="s">
-        <v>275</v>
+        <v>609</v>
+      </c>
+      <c r="S105" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="W105" t="s">
         <v>63</v>
       </c>
       <c r="X105">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>618</v>
+        <v>596</v>
       </c>
       <c r="B106" t="s">
-        <v>619</v>
+        <v>597</v>
       </c>
       <c r="F106" t="s">
-        <v>228</v>
+        <v>598</v>
       </c>
       <c r="G106" t="s">
-        <v>461</v>
+        <v>587</v>
       </c>
       <c r="H106" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="I106" t="s">
-        <v>620</v>
+        <v>59</v>
       </c>
       <c r="J106" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="M106" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="N106" t="s">
-        <v>623</v>
-      </c>
-      <c r="S106" t="s">
-        <v>33</v>
+        <v>612</v>
+      </c>
+      <c r="S106" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="W106" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="X106">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>624</v>
+        <v>596</v>
       </c>
       <c r="B107" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="F107" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
       <c r="G107" t="s">
-        <v>86</v>
+        <v>587</v>
       </c>
       <c r="H107" t="s">
-        <v>627</v>
+        <v>122</v>
       </c>
       <c r="I107" t="s">
-        <v>116</v>
+        <v>613</v>
       </c>
       <c r="J107" t="s">
-        <v>628</v>
+        <v>614</v>
       </c>
       <c r="M107" t="s">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="N107" t="s">
-        <v>630</v>
-      </c>
-      <c r="S107" t="s">
-        <v>491</v>
+        <v>616</v>
+      </c>
+      <c r="S107" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T107" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="W107" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="X107">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>631</v>
+        <v>617</v>
       </c>
       <c r="B108" t="s">
-        <v>632</v>
+        <v>618</v>
       </c>
       <c r="F108" t="s">
-        <v>410</v>
+        <v>227</v>
       </c>
       <c r="G108" t="s">
-        <v>57</v>
+        <v>460</v>
       </c>
       <c r="H108" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I108" t="s">
-        <v>593</v>
+        <v>619</v>
       </c>
       <c r="J108" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="M108" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="N108" t="s">
-        <v>635</v>
-      </c>
-      <c r="S108" t="s">
+        <v>622</v>
+      </c>
+      <c r="S108" s="3" t="s">
         <v>33</v>
       </c>
       <c r="W108" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="X108">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="B109" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="F109" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="G109" t="s">
-        <v>504</v>
+        <v>86</v>
       </c>
       <c r="H109" t="s">
-        <v>328</v>
+        <v>626</v>
       </c>
       <c r="I109" t="s">
-        <v>639</v>
+        <v>116</v>
       </c>
       <c r="J109" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="M109" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="N109" t="s">
-        <v>642</v>
-      </c>
-      <c r="S109" t="s">
-        <v>39</v>
-      </c>
-      <c r="T109" t="s">
-        <v>643</v>
+        <v>629</v>
+      </c>
+      <c r="S109" s="3" t="s">
+        <v>490</v>
       </c>
       <c r="W109" t="s">
-        <v>644</v>
+        <v>114</v>
       </c>
       <c r="X109">
         <v>2</v>
@@ -6906,78 +7101,78 @@
     </row>
     <row r="110" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>127</v>
+        <v>630</v>
       </c>
       <c r="B110" t="s">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c r="F110" t="s">
-        <v>189</v>
+        <v>409</v>
       </c>
       <c r="G110" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="H110" t="s">
-        <v>340</v>
+        <v>215</v>
       </c>
       <c r="I110" t="s">
-        <v>403</v>
+        <v>592</v>
       </c>
       <c r="J110" t="s">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="M110" t="s">
-        <v>647</v>
+        <v>633</v>
       </c>
       <c r="N110" t="s">
-        <v>648</v>
-      </c>
-      <c r="S110" t="s">
-        <v>649</v>
+        <v>634</v>
+      </c>
+      <c r="S110" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="W110" t="s">
-        <v>193</v>
+        <v>114</v>
       </c>
       <c r="X110">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>650</v>
+        <v>635</v>
       </c>
       <c r="B111" t="s">
-        <v>651</v>
+        <v>636</v>
       </c>
       <c r="F111" t="s">
-        <v>46</v>
+        <v>637</v>
       </c>
       <c r="G111" t="s">
-        <v>453</v>
+        <v>503</v>
       </c>
       <c r="H111" t="s">
-        <v>652</v>
+        <v>327</v>
       </c>
       <c r="I111" t="s">
-        <v>79</v>
+        <v>638</v>
       </c>
       <c r="J111" t="s">
-        <v>589</v>
+        <v>639</v>
       </c>
       <c r="M111" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="N111" t="s">
-        <v>654</v>
-      </c>
-      <c r="S111" t="s">
+        <v>641</v>
+      </c>
+      <c r="S111" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T111" t="s">
-        <v>465</v>
+      <c r="T111" s="3" t="s">
+        <v>642</v>
       </c>
       <c r="W111" t="s">
-        <v>53</v>
+        <v>643</v>
       </c>
       <c r="X111">
         <v>2</v>
@@ -6985,37 +7180,37 @@
     </row>
     <row r="112" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>650</v>
+        <v>127</v>
       </c>
       <c r="B112" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="F112" t="s">
-        <v>46</v>
+        <v>188</v>
       </c>
       <c r="G112" t="s">
-        <v>453</v>
+        <v>36</v>
       </c>
       <c r="H112" t="s">
-        <v>655</v>
+        <v>339</v>
+      </c>
+      <c r="I112" t="s">
+        <v>402</v>
       </c>
       <c r="J112" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="M112" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="N112" t="s">
-        <v>658</v>
-      </c>
-      <c r="S112" t="s">
-        <v>39</v>
-      </c>
-      <c r="T112" t="s">
-        <v>659</v>
+        <v>647</v>
+      </c>
+      <c r="S112" s="3" t="s">
+        <v>648</v>
       </c>
       <c r="W112" t="s">
-        <v>53</v>
+        <v>192</v>
       </c>
       <c r="X112">
         <v>3</v>
@@ -7023,37 +7218,40 @@
     </row>
     <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="B113" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="F113" t="s">
-        <v>378</v>
+        <v>46</v>
       </c>
       <c r="G113" t="s">
-        <v>129</v>
+        <v>452</v>
       </c>
       <c r="H113" t="s">
-        <v>581</v>
+        <v>651</v>
       </c>
       <c r="I113" t="s">
-        <v>662</v>
+        <v>79</v>
       </c>
       <c r="J113" t="s">
-        <v>663</v>
+        <v>588</v>
       </c>
       <c r="M113" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="N113" t="s">
-        <v>665</v>
-      </c>
-      <c r="S113" t="s">
-        <v>33</v>
+        <v>653</v>
+      </c>
+      <c r="S113" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T113" s="3" t="s">
+        <v>464</v>
       </c>
       <c r="W113" t="s">
-        <v>666</v>
+        <v>53</v>
       </c>
       <c r="X113">
         <v>2</v>
@@ -7061,157 +7259,157 @@
     </row>
     <row r="114" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>667</v>
+        <v>649</v>
       </c>
       <c r="B114" t="s">
-        <v>668</v>
+        <v>650</v>
       </c>
       <c r="F114" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="G114" t="s">
-        <v>669</v>
+        <v>452</v>
       </c>
       <c r="H114" t="s">
-        <v>670</v>
-      </c>
-      <c r="I114" t="s">
-        <v>403</v>
+        <v>654</v>
       </c>
       <c r="J114" t="s">
-        <v>450</v>
+        <v>655</v>
       </c>
       <c r="M114" t="s">
-        <v>671</v>
+        <v>656</v>
       </c>
       <c r="N114" t="s">
-        <v>672</v>
-      </c>
-      <c r="S114" t="s">
-        <v>33</v>
-      </c>
-      <c r="T114" t="s">
-        <v>374</v>
+        <v>657</v>
+      </c>
+      <c r="S114" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T114" s="3" t="s">
+        <v>658</v>
       </c>
       <c r="W114" t="s">
-        <v>193</v>
+        <v>53</v>
       </c>
       <c r="X114">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="B115" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="F115" t="s">
-        <v>675</v>
+        <v>377</v>
       </c>
       <c r="G115" t="s">
-        <v>460</v>
+        <v>129</v>
       </c>
       <c r="H115" t="s">
-        <v>676</v>
+        <v>580</v>
       </c>
       <c r="I115" t="s">
-        <v>639</v>
+        <v>661</v>
       </c>
       <c r="J115" t="s">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="M115" t="s">
-        <v>678</v>
+        <v>663</v>
       </c>
       <c r="N115" t="s">
-        <v>679</v>
-      </c>
-      <c r="S115" t="s">
-        <v>39</v>
-      </c>
-      <c r="T115" t="s">
-        <v>680</v>
+        <v>664</v>
+      </c>
+      <c r="S115" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="W115" t="s">
-        <v>681</v>
+        <v>665</v>
       </c>
       <c r="X115">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="B116" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="F116" t="s">
-        <v>675</v>
+        <v>86</v>
       </c>
       <c r="G116" t="s">
-        <v>460</v>
+        <v>668</v>
       </c>
       <c r="H116" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="I116" t="s">
-        <v>639</v>
+        <v>402</v>
       </c>
       <c r="J116" t="s">
-        <v>683</v>
+        <v>449</v>
       </c>
       <c r="M116" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="N116" t="s">
-        <v>685</v>
-      </c>
-      <c r="S116" t="s">
-        <v>39</v>
-      </c>
-      <c r="T116" t="s">
-        <v>686</v>
+        <v>671</v>
+      </c>
+      <c r="S116" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T116" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="W116" t="s">
-        <v>681</v>
+        <v>192</v>
       </c>
       <c r="X116">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>376</v>
+        <v>672</v>
       </c>
       <c r="B117" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="F117" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="G117" t="s">
-        <v>115</v>
+        <v>459</v>
       </c>
       <c r="H117" t="s">
-        <v>178</v>
+        <v>675</v>
+      </c>
+      <c r="I117" t="s">
+        <v>638</v>
       </c>
       <c r="J117" t="s">
-        <v>689</v>
+        <v>676</v>
       </c>
       <c r="M117" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="N117" t="s">
-        <v>691</v>
-      </c>
-      <c r="S117" t="s">
+        <v>678</v>
+      </c>
+      <c r="S117" s="3" t="s">
         <v>39</v>
       </c>
+      <c r="T117" s="3" t="s">
+        <v>679</v>
+      </c>
       <c r="W117" t="s">
-        <v>253</v>
+        <v>680</v>
       </c>
       <c r="X117">
         <v>3</v>
@@ -7219,78 +7417,75 @@
     </row>
     <row r="118" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>692</v>
+        <v>672</v>
       </c>
       <c r="B118" t="s">
-        <v>693</v>
+        <v>673</v>
       </c>
       <c r="F118" t="s">
-        <v>694</v>
+        <v>674</v>
       </c>
       <c r="G118" t="s">
-        <v>695</v>
+        <v>459</v>
       </c>
       <c r="H118" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="I118" t="s">
-        <v>697</v>
+        <v>638</v>
       </c>
       <c r="J118" t="s">
-        <v>698</v>
+        <v>682</v>
       </c>
       <c r="M118" t="s">
-        <v>699</v>
+        <v>683</v>
       </c>
       <c r="N118" t="s">
-        <v>700</v>
-      </c>
-      <c r="S118" t="s">
-        <v>33</v>
+        <v>684</v>
+      </c>
+      <c r="S118" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T118" s="3" t="s">
+        <v>685</v>
       </c>
       <c r="W118" t="s">
-        <v>522</v>
+        <v>680</v>
       </c>
       <c r="X118">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>701</v>
+        <v>375</v>
       </c>
       <c r="B119" t="s">
-        <v>702</v>
+        <v>686</v>
       </c>
       <c r="F119" t="s">
-        <v>225</v>
+        <v>687</v>
       </c>
       <c r="G119" t="s">
-        <v>703</v>
+        <v>115</v>
       </c>
       <c r="H119" t="s">
-        <v>704</v>
-      </c>
-      <c r="I119" t="s">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="J119" t="s">
-        <v>565</v>
+        <v>688</v>
       </c>
       <c r="M119" t="s">
-        <v>705</v>
+        <v>689</v>
       </c>
       <c r="N119" t="s">
-        <v>706</v>
-      </c>
-      <c r="S119" t="s">
+        <v>690</v>
+      </c>
+      <c r="S119" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T119" t="s">
-        <v>177</v>
-      </c>
       <c r="W119" t="s">
-        <v>114</v>
+        <v>252</v>
       </c>
       <c r="X119">
         <v>3</v>
@@ -7298,37 +7493,37 @@
     </row>
     <row r="120" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="B120" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="F120" t="s">
-        <v>225</v>
+        <v>693</v>
       </c>
       <c r="G120" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
       <c r="H120" t="s">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="I120" t="s">
-        <v>708</v>
+        <v>696</v>
       </c>
       <c r="J120" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="M120" t="s">
-        <v>710</v>
+        <v>698</v>
       </c>
       <c r="N120" t="s">
-        <v>711</v>
-      </c>
-      <c r="S120" t="s">
-        <v>712</v>
+        <v>699</v>
+      </c>
+      <c r="S120" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="W120" t="s">
-        <v>114</v>
+        <v>521</v>
       </c>
       <c r="X120">
         <v>2</v>
@@ -7336,43 +7531,126 @@
     </row>
     <row r="121" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>700</v>
+      </c>
+      <c r="B121" t="s">
+        <v>701</v>
+      </c>
+      <c r="F121" t="s">
+        <v>224</v>
+      </c>
+      <c r="G121" t="s">
+        <v>702</v>
+      </c>
+      <c r="H121" t="s">
+        <v>703</v>
+      </c>
+      <c r="I121" t="s">
+        <v>116</v>
+      </c>
+      <c r="J121" t="s">
+        <v>564</v>
+      </c>
+      <c r="M121" t="s">
+        <v>704</v>
+      </c>
+      <c r="N121" t="s">
+        <v>705</v>
+      </c>
+      <c r="S121" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T121" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="W121" t="s">
+        <v>114</v>
+      </c>
+      <c r="X121">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>700</v>
+      </c>
+      <c r="B122" t="s">
+        <v>701</v>
+      </c>
+      <c r="F122" t="s">
+        <v>224</v>
+      </c>
+      <c r="G122" t="s">
+        <v>702</v>
+      </c>
+      <c r="H122" t="s">
+        <v>706</v>
+      </c>
+      <c r="I122" t="s">
+        <v>707</v>
+      </c>
+      <c r="J122" t="s">
+        <v>708</v>
+      </c>
+      <c r="M122" t="s">
+        <v>709</v>
+      </c>
+      <c r="N122" t="s">
+        <v>710</v>
+      </c>
+      <c r="S122" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="W122" t="s">
+        <v>114</v>
+      </c>
+      <c r="X122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>712</v>
+      </c>
+      <c r="B123" t="s">
         <v>713</v>
       </c>
-      <c r="B121" t="s">
+      <c r="F123" t="s">
+        <v>681</v>
+      </c>
+      <c r="G123" t="s">
         <v>714</v>
       </c>
-      <c r="F121" t="s">
-        <v>682</v>
-      </c>
-      <c r="G121" t="s">
+      <c r="H123" t="s">
+        <v>48</v>
+      </c>
+      <c r="I123" t="s">
+        <v>49</v>
+      </c>
+      <c r="J123" t="s">
         <v>715</v>
       </c>
-      <c r="H121" t="s">
-        <v>48</v>
-      </c>
-      <c r="I121" t="s">
-        <v>49</v>
-      </c>
-      <c r="J121" t="s">
+      <c r="M123" t="s">
         <v>716</v>
       </c>
-      <c r="M121" t="s">
+      <c r="N123" t="s">
         <v>717</v>
       </c>
-      <c r="N121" t="s">
-        <v>718</v>
-      </c>
-      <c r="S121" t="s">
+      <c r="S123" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="W121" t="s">
+      <c r="W123" t="s">
         <v>53</v>
       </c>
-      <c r="X121">
+      <c r="X123">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="N21" r:id="rId1" xr:uid="{347500AD-78A8-4CDD-952C-E47BD4F93F86}"/>
+    <hyperlink ref="N22" r:id="rId2" xr:uid="{7157D416-FEAD-4926-9F17-F376F79B410A}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>